--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\market_insights\outputs\run_generated_281225_at_07.09\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\market_insights\outputs\run_generated_311225_at_15.57\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19BCDAA-429F-44E7-B0A6-88EF94F52555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAB4208-247A-4ADE-9FF1-EE268B07B599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="696" yWindow="3132" windowWidth="15408" windowHeight="7620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="THREAT_ALERT" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="47">
   <si>
     <t>Date</t>
   </si>
@@ -60,16 +60,16 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>28-DEC-25</t>
+    <t>04-JAN-26</t>
   </si>
   <si>
     <t>SM-463</t>
   </si>
   <si>
-    <t>flyadeal F3-612</t>
-  </si>
-  <si>
-    <t>LOW</t>
+    <t>flyadeal F3-606</t>
+  </si>
+  <si>
+    <t>LOW THREAT</t>
   </si>
   <si>
     <t>EGP</t>
@@ -78,75 +78,84 @@
     <t>flyadeal F3-616</t>
   </si>
   <si>
-    <t>flyadeal F3-608</t>
-  </si>
-  <si>
-    <t>flyadeal F3-606</t>
+    <t>Air Arabia Egypt E5-410</t>
+  </si>
+  <si>
+    <t>Air Arabia Egypt E5-415</t>
+  </si>
+  <si>
+    <t>06-JAN-26</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-160</t>
+  </si>
+  <si>
+    <t>flynas XY-266</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-649</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-651</t>
+  </si>
+  <si>
+    <t>Saudia SV-320</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-647</t>
+  </si>
+  <si>
+    <t>Saudia SV-324</t>
+  </si>
+  <si>
+    <t>Saudia SV-312</t>
+  </si>
+  <si>
+    <t>Saudia SV-418</t>
+  </si>
+  <si>
+    <t>flynas XY-284</t>
+  </si>
+  <si>
+    <t>07-JAN-26</t>
+  </si>
+  <si>
+    <t>SM-465</t>
+  </si>
+  <si>
+    <t>Nile Air NP-251</t>
+  </si>
+  <si>
+    <t>flynas XY-268</t>
+  </si>
+  <si>
+    <t>flynas XY-264</t>
+  </si>
+  <si>
+    <t>flynas XY-274</t>
+  </si>
+  <si>
+    <t>flynas XY-270</t>
+  </si>
+  <si>
+    <t>flynas XY-276</t>
+  </si>
+  <si>
+    <t>flynas XY-272</t>
+  </si>
+  <si>
+    <t>Saudia SV-310</t>
+  </si>
+  <si>
+    <t>11-JAN-26</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-162</t>
   </si>
   <si>
     <t>Nile Air NP-151</t>
   </si>
   <si>
-    <t>flynas XY-266</t>
-  </si>
-  <si>
-    <t>flynas XY-272</t>
-  </si>
-  <si>
-    <t>30-DEC-25</t>
-  </si>
-  <si>
-    <t>Air Arabia Egypt E5-415</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-160</t>
-  </si>
-  <si>
-    <t>Air Arabia Egypt E5-410</t>
-  </si>
-  <si>
-    <t>flynas XY-274</t>
-  </si>
-  <si>
-    <t>flynas XY-270</t>
-  </si>
-  <si>
-    <t>Saudia SV-324</t>
-  </si>
-  <si>
-    <t>Saudia SV-312</t>
-  </si>
-  <si>
-    <t>06-JAN-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-649</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-651</t>
-  </si>
-  <si>
-    <t>flynas XY-284</t>
-  </si>
-  <si>
-    <t>07-JAN-26</t>
-  </si>
-  <si>
-    <t>SM-465</t>
-  </si>
-  <si>
-    <t>Nile Air NP-251</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-647</t>
-  </si>
-  <si>
-    <t>Saudia SV-310</t>
-  </si>
-  <si>
-    <t>11-JAN-26</t>
-  </si>
-  <si>
     <t>13-JAN-26</t>
   </si>
   <si>
@@ -154,6 +163,9 @@
   </si>
   <si>
     <t>18-JAN-26</t>
+  </si>
+  <si>
+    <t>20-JAN-26</t>
   </si>
 </sst>
 </file>
@@ -541,7 +553,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -552,7 +564,7 @@
     <col min="7" max="7" width="153.44140625" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="8" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -602,13 +614,13 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>5060</v>
+        <v>7340</v>
       </c>
       <c r="E2" s="2">
-        <v>10628</v>
+        <v>12196</v>
       </c>
       <c r="F2" s="2">
-        <v>-5568</v>
+        <v>-4856</v>
       </c>
       <c r="G2" s="2">
         <v>15</v>
@@ -637,13 +649,13 @@
         <v>16</v>
       </c>
       <c r="D3" s="2">
-        <v>5060</v>
+        <v>7340</v>
       </c>
       <c r="E3" s="2">
-        <v>10628</v>
+        <v>12196</v>
       </c>
       <c r="F3" s="2">
-        <v>-5568</v>
+        <v>-4856</v>
       </c>
       <c r="G3" s="2">
         <v>15</v>
@@ -672,22 +684,22 @@
         <v>17</v>
       </c>
       <c r="D4" s="2">
-        <v>5440</v>
+        <v>7564</v>
       </c>
       <c r="E4" s="2">
-        <v>10628</v>
+        <v>12196</v>
       </c>
       <c r="F4" s="2">
-        <v>-5188</v>
+        <v>-4632</v>
       </c>
       <c r="G4" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2">
         <v>30</v>
       </c>
       <c r="I4" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>14</v>
@@ -707,22 +719,22 @@
         <v>18</v>
       </c>
       <c r="D5" s="2">
-        <v>5440</v>
+        <v>9199</v>
       </c>
       <c r="E5" s="2">
-        <v>10628</v>
+        <v>12196</v>
       </c>
       <c r="F5" s="2">
-        <v>-5188</v>
+        <v>-2997</v>
       </c>
       <c r="G5" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2">
         <v>30</v>
       </c>
       <c r="I5" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>14</v>
@@ -733,22 +745,22 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2">
-        <v>6683</v>
+        <v>5591</v>
       </c>
       <c r="E6" s="2">
-        <v>10628</v>
+        <v>9407</v>
       </c>
       <c r="F6" s="2">
-        <v>-3945</v>
+        <v>-3816</v>
       </c>
       <c r="G6" s="2">
         <v>30</v>
@@ -768,22 +780,22 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2">
-        <v>7470</v>
+        <v>5930</v>
       </c>
       <c r="E7" s="2">
-        <v>10628</v>
+        <v>9407</v>
       </c>
       <c r="F7" s="2">
-        <v>-3158</v>
+        <v>-3477</v>
       </c>
       <c r="G7" s="2">
         <v>30</v>
@@ -803,22 +815,22 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D8" s="2">
-        <v>7470</v>
+        <v>6072</v>
       </c>
       <c r="E8" s="2">
-        <v>10628</v>
+        <v>9407</v>
       </c>
       <c r="F8" s="2">
-        <v>-3158</v>
+        <v>-3335</v>
       </c>
       <c r="G8" s="2">
         <v>30</v>
@@ -838,22 +850,22 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2">
-        <v>6170</v>
+        <v>6833</v>
       </c>
       <c r="E9" s="2">
-        <v>9423</v>
+        <v>9407</v>
       </c>
       <c r="F9" s="2">
-        <v>-3253</v>
+        <v>-2574</v>
       </c>
       <c r="G9" s="2">
         <v>30</v>
@@ -873,31 +885,31 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="D10" s="2">
-        <v>6239</v>
+        <v>8101</v>
       </c>
       <c r="E10" s="2">
-        <v>9423</v>
+        <v>9407</v>
       </c>
       <c r="F10" s="2">
-        <v>-3184</v>
+        <v>-1306</v>
       </c>
       <c r="G10" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2">
         <v>30</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>14</v>
@@ -908,31 +920,31 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" s="2">
-        <v>6786</v>
+        <v>8101</v>
       </c>
       <c r="E11" s="2">
-        <v>9423</v>
+        <v>9407</v>
       </c>
       <c r="F11" s="2">
-        <v>-2637</v>
+        <v>-1306</v>
       </c>
       <c r="G11" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2">
         <v>30</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>14</v>
@@ -943,31 +955,31 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2">
-        <v>6836</v>
+        <v>8634</v>
       </c>
       <c r="E12" s="2">
-        <v>9423</v>
+        <v>9407</v>
       </c>
       <c r="F12" s="2">
-        <v>-2587</v>
+        <v>-773</v>
       </c>
       <c r="G12" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2">
         <v>30</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>14</v>
@@ -978,31 +990,31 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2">
-        <v>6836</v>
+        <v>8824</v>
       </c>
       <c r="E13" s="2">
-        <v>9423</v>
+        <v>9407</v>
       </c>
       <c r="F13" s="2">
-        <v>-2587</v>
+        <v>-583</v>
       </c>
       <c r="G13" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2">
         <v>30</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>14</v>
@@ -1013,31 +1025,31 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" s="2">
-        <v>6836</v>
+        <v>9242</v>
       </c>
       <c r="E14" s="2">
-        <v>9423</v>
+        <v>9407</v>
       </c>
       <c r="F14" s="2">
-        <v>-2587</v>
+        <v>-165</v>
       </c>
       <c r="G14" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2">
         <v>30</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>14</v>
@@ -1048,22 +1060,22 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" s="2">
-        <v>9055</v>
+        <v>9242</v>
       </c>
       <c r="E15" s="2">
-        <v>9423</v>
+        <v>9407</v>
       </c>
       <c r="F15" s="2">
-        <v>-368</v>
+        <v>-165</v>
       </c>
       <c r="G15" s="2">
         <v>46</v>
@@ -1083,22 +1095,22 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" s="2">
-        <v>9055</v>
+        <v>9242</v>
       </c>
       <c r="E16" s="2">
-        <v>9423</v>
+        <v>9407</v>
       </c>
       <c r="F16" s="2">
-        <v>-368</v>
+        <v>-165</v>
       </c>
       <c r="G16" s="2">
         <v>46</v>
@@ -1118,31 +1130,31 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D17" s="2">
-        <v>5269</v>
+        <v>9901</v>
       </c>
       <c r="E17" s="2">
-        <v>8624</v>
+        <v>9407</v>
       </c>
       <c r="F17" s="2">
-        <v>-3355</v>
+        <v>494</v>
       </c>
       <c r="G17" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H17" s="2">
         <v>30</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>14</v>
@@ -1156,19 +1168,19 @@
         <v>30</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D18" s="2">
-        <v>5506</v>
+        <v>5266</v>
       </c>
       <c r="E18" s="2">
-        <v>8624</v>
+        <v>9407</v>
       </c>
       <c r="F18" s="2">
-        <v>-3118</v>
+        <v>-4141</v>
       </c>
       <c r="G18" s="2">
         <v>30</v>
@@ -1191,19 +1203,19 @@
         <v>30</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D19" s="2">
-        <v>5605</v>
+        <v>6047</v>
       </c>
       <c r="E19" s="2">
-        <v>8624</v>
+        <v>9407</v>
       </c>
       <c r="F19" s="2">
-        <v>-3019</v>
+        <v>-3360</v>
       </c>
       <c r="G19" s="2">
         <v>30</v>
@@ -1226,19 +1238,19 @@
         <v>30</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D20" s="2">
-        <v>6049</v>
+        <v>6199</v>
       </c>
       <c r="E20" s="2">
-        <v>8624</v>
+        <v>9407</v>
       </c>
       <c r="F20" s="2">
-        <v>-2575</v>
+        <v>-3208</v>
       </c>
       <c r="G20" s="2">
         <v>30</v>
@@ -1261,28 +1273,28 @@
         <v>30</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D21" s="2">
-        <v>7000</v>
+        <v>6199</v>
       </c>
       <c r="E21" s="2">
-        <v>8624</v>
+        <v>9407</v>
       </c>
       <c r="F21" s="2">
-        <v>-1624</v>
+        <v>-3208</v>
       </c>
       <c r="G21" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2">
         <v>30</v>
       </c>
       <c r="I21" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>14</v>
@@ -1296,28 +1308,28 @@
         <v>30</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D22" s="2">
-        <v>7558</v>
+        <v>6199</v>
       </c>
       <c r="E22" s="2">
-        <v>8624</v>
+        <v>9407</v>
       </c>
       <c r="F22" s="2">
-        <v>-1066</v>
+        <v>-3208</v>
       </c>
       <c r="G22" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H22" s="2">
         <v>30</v>
       </c>
       <c r="I22" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>14</v>
@@ -1331,28 +1343,28 @@
         <v>30</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D23" s="2">
-        <v>9905</v>
+        <v>6199</v>
       </c>
       <c r="E23" s="2">
-        <v>8624</v>
+        <v>9407</v>
       </c>
       <c r="F23" s="2">
-        <v>1281</v>
+        <v>-3208</v>
       </c>
       <c r="G23" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H23" s="2">
         <v>30</v>
       </c>
       <c r="I23" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>14</v>
@@ -1363,22 +1375,22 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D24" s="2">
-        <v>5631</v>
+        <v>6833</v>
       </c>
       <c r="E24" s="2">
-        <v>8624</v>
+        <v>9407</v>
       </c>
       <c r="F24" s="2">
-        <v>-2993</v>
+        <v>-2574</v>
       </c>
       <c r="G24" s="2">
         <v>30</v>
@@ -1398,22 +1410,22 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D25" s="2">
-        <v>5631</v>
+        <v>6833</v>
       </c>
       <c r="E25" s="2">
-        <v>8624</v>
+        <v>9407</v>
       </c>
       <c r="F25" s="2">
-        <v>-2993</v>
+        <v>-2574</v>
       </c>
       <c r="G25" s="2">
         <v>30</v>
@@ -1433,22 +1445,22 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D26" s="2">
-        <v>5743</v>
+        <v>6833</v>
       </c>
       <c r="E26" s="2">
-        <v>8624</v>
+        <v>9407</v>
       </c>
       <c r="F26" s="2">
-        <v>-2881</v>
+        <v>-2574</v>
       </c>
       <c r="G26" s="2">
         <v>30</v>
@@ -1468,22 +1480,22 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D27" s="2">
-        <v>7000</v>
+        <v>8634</v>
       </c>
       <c r="E27" s="2">
-        <v>8624</v>
+        <v>9407</v>
       </c>
       <c r="F27" s="2">
-        <v>-1624</v>
+        <v>-773</v>
       </c>
       <c r="G27" s="2">
         <v>46</v>
@@ -1503,22 +1515,22 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D28" s="2">
-        <v>7000</v>
+        <v>8634</v>
       </c>
       <c r="E28" s="2">
-        <v>8624</v>
+        <v>9407</v>
       </c>
       <c r="F28" s="2">
-        <v>-1624</v>
+        <v>-773</v>
       </c>
       <c r="G28" s="2">
         <v>46</v>
@@ -1538,22 +1550,22 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D29" s="2">
-        <v>8117</v>
+        <v>8824</v>
       </c>
       <c r="E29" s="2">
-        <v>8624</v>
+        <v>9407</v>
       </c>
       <c r="F29" s="2">
-        <v>-507</v>
+        <v>-583</v>
       </c>
       <c r="G29" s="2">
         <v>46</v>
@@ -1573,22 +1585,22 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D30" s="2">
-        <v>8434</v>
+        <v>9242</v>
       </c>
       <c r="E30" s="2">
-        <v>8624</v>
+        <v>9407</v>
       </c>
       <c r="F30" s="2">
-        <v>-190</v>
+        <v>-165</v>
       </c>
       <c r="G30" s="2">
         <v>46</v>
@@ -1608,22 +1620,22 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D31" s="2">
-        <v>6480</v>
+        <v>9242</v>
       </c>
       <c r="E31" s="2">
-        <v>7153</v>
+        <v>9407</v>
       </c>
       <c r="F31" s="2">
-        <v>-673</v>
+        <v>-165</v>
       </c>
       <c r="G31" s="2">
         <v>46</v>
@@ -1643,31 +1655,31 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D32" s="2">
-        <v>6582</v>
+        <v>5100</v>
       </c>
       <c r="E32" s="2">
-        <v>7153</v>
+        <v>8608</v>
       </c>
       <c r="F32" s="2">
-        <v>-571</v>
+        <v>-3508</v>
       </c>
       <c r="G32" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2">
         <v>30</v>
       </c>
       <c r="I32" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>14</v>
@@ -1684,25 +1696,25 @@
         <v>12</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D33" s="2">
-        <v>7000</v>
+        <v>5337</v>
       </c>
       <c r="E33" s="2">
-        <v>7812</v>
+        <v>8608</v>
       </c>
       <c r="F33" s="2">
-        <v>-812</v>
+        <v>-3271</v>
       </c>
       <c r="G33" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2">
         <v>30</v>
       </c>
       <c r="I33" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>14</v>
@@ -1719,25 +1731,25 @@
         <v>12</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D34" s="2">
-        <v>7000</v>
+        <v>5591</v>
       </c>
       <c r="E34" s="2">
-        <v>7812</v>
+        <v>8608</v>
       </c>
       <c r="F34" s="2">
-        <v>-812</v>
+        <v>-3017</v>
       </c>
       <c r="G34" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H34" s="2">
         <v>30</v>
       </c>
       <c r="I34" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>14</v>
@@ -1754,25 +1766,25 @@
         <v>12</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D35" s="2">
-        <v>7102</v>
+        <v>5629</v>
       </c>
       <c r="E35" s="2">
-        <v>7812</v>
+        <v>8608</v>
       </c>
       <c r="F35" s="2">
-        <v>-710</v>
+        <v>-2979</v>
       </c>
       <c r="G35" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2">
         <v>30</v>
       </c>
       <c r="I35" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>14</v>
@@ -1783,22 +1795,22 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D36" s="2">
-        <v>5605</v>
+        <v>5692</v>
       </c>
       <c r="E36" s="2">
-        <v>8624</v>
+        <v>8608</v>
       </c>
       <c r="F36" s="2">
-        <v>-3019</v>
+        <v>-2916</v>
       </c>
       <c r="G36" s="2">
         <v>30</v>
@@ -1818,22 +1830,22 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D37" s="2">
-        <v>6049</v>
+        <v>5692</v>
       </c>
       <c r="E37" s="2">
-        <v>8624</v>
+        <v>8608</v>
       </c>
       <c r="F37" s="2">
-        <v>-2575</v>
+        <v>-2916</v>
       </c>
       <c r="G37" s="2">
         <v>30</v>
@@ -1853,31 +1865,31 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D38" s="2">
-        <v>7558</v>
+        <v>5692</v>
       </c>
       <c r="E38" s="2">
-        <v>8624</v>
+        <v>8608</v>
       </c>
       <c r="F38" s="2">
-        <v>-1066</v>
+        <v>-2916</v>
       </c>
       <c r="G38" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H38" s="2">
         <v>30</v>
       </c>
       <c r="I38" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>14</v>
@@ -1888,31 +1900,31 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="D39" s="2">
-        <v>8434</v>
+        <v>5692</v>
       </c>
       <c r="E39" s="2">
-        <v>8624</v>
+        <v>8608</v>
       </c>
       <c r="F39" s="2">
-        <v>-190</v>
+        <v>-2916</v>
       </c>
       <c r="G39" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H39" s="2">
         <v>30</v>
       </c>
       <c r="I39" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>14</v>
@@ -1923,36 +1935,456 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40" s="2">
+        <v>5692</v>
+      </c>
+      <c r="E40" s="2">
+        <v>8608</v>
+      </c>
+      <c r="F40" s="2">
+        <v>-2916</v>
+      </c>
+      <c r="G40" s="2">
+        <v>30</v>
+      </c>
+      <c r="H40" s="2">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="2">
+        <v>6985</v>
+      </c>
+      <c r="E41" s="2">
+        <v>8608</v>
+      </c>
+      <c r="F41" s="2">
+        <v>-1623</v>
+      </c>
+      <c r="G41" s="2">
+        <v>46</v>
+      </c>
+      <c r="H41" s="2">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2">
+        <v>-16</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="2">
+        <v>7087</v>
+      </c>
+      <c r="E42" s="2">
+        <v>8608</v>
+      </c>
+      <c r="F42" s="2">
+        <v>-1521</v>
+      </c>
+      <c r="G42" s="2">
+        <v>46</v>
+      </c>
+      <c r="H42" s="2">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2">
+        <v>-16</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="2">
+        <v>7911</v>
+      </c>
+      <c r="E43" s="2">
+        <v>8608</v>
+      </c>
+      <c r="F43" s="2">
+        <v>-697</v>
+      </c>
+      <c r="G43" s="2">
+        <v>46</v>
+      </c>
+      <c r="H43" s="2">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2">
+        <v>-16</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="2">
+        <v>8203</v>
+      </c>
+      <c r="E44" s="2">
+        <v>8608</v>
+      </c>
+      <c r="F44" s="2">
+        <v>-405</v>
+      </c>
+      <c r="G44" s="2">
+        <v>46</v>
+      </c>
+      <c r="H44" s="2">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2">
+        <v>-16</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="2">
+        <v>4564</v>
+      </c>
+      <c r="E45" s="2">
+        <v>8608</v>
+      </c>
+      <c r="F45" s="2">
+        <v>-4044</v>
+      </c>
+      <c r="G45" s="2">
+        <v>30</v>
+      </c>
+      <c r="H45" s="2">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="2">
+        <v>4792</v>
+      </c>
+      <c r="E46" s="2">
+        <v>8608</v>
+      </c>
+      <c r="F46" s="2">
+        <v>-3816</v>
+      </c>
+      <c r="G46" s="2">
+        <v>30</v>
+      </c>
+      <c r="H46" s="2">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="2">
+        <v>5029</v>
+      </c>
+      <c r="E47" s="2">
+        <v>8608</v>
+      </c>
+      <c r="F47" s="2">
+        <v>-3579</v>
+      </c>
+      <c r="G47" s="2">
+        <v>30</v>
+      </c>
+      <c r="H47" s="2">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" s="2">
+        <v>8101</v>
+      </c>
+      <c r="E48" s="2">
+        <v>8608</v>
+      </c>
+      <c r="F48" s="2">
+        <v>-507</v>
+      </c>
+      <c r="G48" s="2">
+        <v>46</v>
+      </c>
+      <c r="H48" s="2">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2">
+        <v>-16</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D40" s="2">
-        <v>8117</v>
-      </c>
-      <c r="E40" s="2">
-        <v>8624</v>
-      </c>
-      <c r="F40" s="2">
-        <v>-507</v>
-      </c>
-      <c r="G40" s="2">
+      <c r="C49" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="2">
+        <v>5029</v>
+      </c>
+      <c r="E49" s="2">
+        <v>8608</v>
+      </c>
+      <c r="F49" s="2">
+        <v>-3579</v>
+      </c>
+      <c r="G49" s="2">
+        <v>30</v>
+      </c>
+      <c r="H49" s="2">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="2">
+        <v>6285</v>
+      </c>
+      <c r="E50" s="2">
+        <v>9407</v>
+      </c>
+      <c r="F50" s="2">
+        <v>-3122</v>
+      </c>
+      <c r="G50" s="2">
+        <v>30</v>
+      </c>
+      <c r="H50" s="2">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H40" s="2">
-        <v>30</v>
-      </c>
-      <c r="I40" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K40" s="2" t="s">
+      <c r="B51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="2">
+        <v>5266</v>
+      </c>
+      <c r="E51" s="2">
+        <v>8608</v>
+      </c>
+      <c r="F51" s="2">
+        <v>-3342</v>
+      </c>
+      <c r="G51" s="2">
+        <v>30</v>
+      </c>
+      <c r="H51" s="2">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="2">
+        <v>5266</v>
+      </c>
+      <c r="E52" s="2">
+        <v>8608</v>
+      </c>
+      <c r="F52" s="2">
+        <v>-3342</v>
+      </c>
+      <c r="G52" s="2">
+        <v>30</v>
+      </c>
+      <c r="H52" s="2">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K52" s="2" t="s">
         <v>15</v>
       </c>
     </row>

--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -48,8 +48,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -459,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -523,27 +541,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>18-MAR-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-465</t>
+          <t>SM-463</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-360</t>
+          <t>Nile Air NP-253</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5042</v>
+        <v>8877</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5131</v>
+        <v>15756</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-89</v>
+        <v>-6879</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -556,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -578,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-415</t>
+          <t>Nile Air NP-251</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>12044</v>
+        <v>8877</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>15343</v>
+        <v>15756</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3299</v>
+        <v>-6879</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -601,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -623,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-410</t>
+          <t>Nile Air NP-151</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>12044</v>
+        <v>8877</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15343</v>
+        <v>15756</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3299</v>
+        <v>-6879</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -646,10 +664,4015 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>24-MAR-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-463</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-160</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>9277</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>15756</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-6479</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>24-MAR-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-463</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-415</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>9356</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>15756</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-6400</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>24-MAR-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-463</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-410</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>10933</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>15756</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-4823</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
           <t>LOW THREAT</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-266</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>9773</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>16583</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-6810</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-270</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>9773</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>16583</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-6810</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-251</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>10145</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>16583</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-6438</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-268</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>11014</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>16583</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-5569</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-272</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>11014</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>16583</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-5569</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-264</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>11014</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>16583</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-5569</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-274</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>11014</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>16583</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-5569</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-606</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>11290</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>16583</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-5293</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-614</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>11290</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>16583</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-5293</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-164</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>12186</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>16583</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-4397</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-608</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>5913</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-8299</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-606</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>5913</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-8299</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-616</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>5913</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-8299</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-614</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>5913</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-8299</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-266</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>6051</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-8161</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-264</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>6051</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-8161</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-274</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>6051</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-8161</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-270</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>6051</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-8161</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-276</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>6878</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-7334</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-268</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>6878</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-7334</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-272</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>6878</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-7334</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-164</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>6906</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-7306</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-160</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>6906</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-7306</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-415</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>7241</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-6971</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-410</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>7241</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-6971</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-251</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>7692</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-6520</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-649</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>8119</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-6093</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-320</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>8174</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-6038</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-310</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>8174</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-6038</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-312</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>8174</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-6038</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-418</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>8174</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-6038</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>8533</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-5679</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-647</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>9001</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-5211</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-606</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>4535</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-9677</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-616</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>4535</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-9677</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-608</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>4948</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-9264</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-614</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>4948</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-9264</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-266</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>5362</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-8850</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-276</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>5362</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-8850</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-268</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>5362</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-8850</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-272</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>5362</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-8850</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-264</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>5362</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-8850</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-274</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>5362</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-8850</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-270</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>5362</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-8850</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-164</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>5679</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-8533</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-160</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>5679</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-8533</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-320</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>6354</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-7858</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-310</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>6354</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-7858</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-418</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>6354</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-7858</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-415</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>6726</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-7486</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-410</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>6726</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-7486</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-251</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>7692</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-6520</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-649</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>7705</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-6507</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>8119</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-6093</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-312</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>8174</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-6038</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-647</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>8588</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>14212</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-5624</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-608</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>4535</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-6520</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-606</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>4535</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-6520</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-616</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>4535</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-6520</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-614</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>4535</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>-6520</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-266</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>4811</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>-6244</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-268</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>4811</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-6244</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-264</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>4811</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>-6244</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-274</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>4811</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>-6244</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-270</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>4811</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>-6244</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-276</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>5362</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>-5693</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-272</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>5362</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-5693</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-320</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>5734</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>-5321</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-310</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>5734</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>-5321</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-312</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>6354</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>-4701</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-418</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>6354</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>-4701</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-415</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>6726</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>-4329</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-410</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>6726</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>-4329</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-649</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>7319</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>-3736</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>22-APR-26</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>7705</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>11055</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>-3350</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-160</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>4673</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>9070</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>-4397</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-266</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>4811</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>9070</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>-4259</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-268</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>4811</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>9070</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>-4259</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-272</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>4811</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>9070</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>-4259</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-264</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>4811</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>9070</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>-4259</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-274</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>4811</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>9070</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>-4259</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-270</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>4811</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>9070</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>-4259</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-310</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>5072</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>9070</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>-3998</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-164</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>5679</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>9070</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>-3391</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>7319</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>9070</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>-1751</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>29-APR-26</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-647</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>8202</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>9070</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-868</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,20 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -477,7 +468,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -541,27 +532,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>24-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-463</t>
+          <t>SM-989</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-253</t>
+          <t>Nile Air NP-251</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8877</v>
+        <v>11321</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>15756</v>
+        <v>14365</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-6879</v>
+        <v>-3044</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -574,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,27 +577,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>24-MAR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-463</t>
+          <t>SM-989</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-251</t>
+          <t>Nile Air NP-151</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8877</v>
+        <v>11321</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>15756</v>
+        <v>14365</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-6879</v>
+        <v>-3044</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -619,7 +610,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,27 +622,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-463</t>
+          <t>SM-465</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-151</t>
+          <t>Nile Air NP-251</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8877</v>
+        <v>10269</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15756</v>
+        <v>14646</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-6879</v>
+        <v>-4377</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -664,7 +655,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,27 +667,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>24-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-463</t>
+          <t>SM-465</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-160</t>
+          <t>Nesma Airlines NE-164</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9277</v>
+        <v>11068</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>15756</v>
+        <v>14646</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-6479</v>
+        <v>-3578</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -709,7 +700,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,27 +712,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-463</t>
+          <t>SM-465</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-415</t>
+          <t>Air Arabia Egypt E5-410</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9356</v>
+        <v>11458</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15756</v>
+        <v>14646</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-6400</v>
+        <v>-3188</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,27 +757,27 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24-MAR-26</t>
+          <t>01-APR-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SM-463</t>
+          <t>SM-465</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-410</t>
+          <t>Air Arabia Egypt E5-415</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>10933</v>
+        <v>11459</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>15756</v>
+        <v>14646</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4823</v>
+        <v>-3187</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -797,7 +788,7 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -811,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,28 +812,28 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>flyadeal F3-608</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9773</v>
+        <v>6860</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>16583</v>
+        <v>14646</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-6810</v>
+        <v>-7786</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -856,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,28 +857,28 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>9773</v>
+        <v>6860</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>16583</v>
+        <v>14646</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-6810</v>
+        <v>-7786</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -901,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +902,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-251</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10145</v>
+        <v>6860</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>16583</v>
+        <v>14646</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-6438</v>
+        <v>-7786</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,28 +947,28 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>11014</v>
+        <v>6860</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>16583</v>
+        <v>14646</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-5569</v>
+        <v>-7786</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -991,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +992,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>Nesma Airlines NE-160</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11014</v>
+        <v>7631</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>16583</v>
+        <v>14646</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-5569</v>
+        <v>-7015</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1037,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>Nesma Airlines NE-164</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>11014</v>
+        <v>8080</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>16583</v>
+        <v>14646</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-5569</v>
+        <v>-6566</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1082,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11014</v>
+        <v>8122</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16583</v>
+        <v>14646</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-5569</v>
+        <v>-6524</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>20</v>
@@ -1112,7 +1103,7 @@
       <c r="I14" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1126,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1127,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>Nile Air NP-251</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>11290</v>
+        <v>8305</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16583</v>
+        <v>14646</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-5293</v>
+        <v>-6341</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,28 +1172,28 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>Saudia SV-320</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>11290</v>
+        <v>8431</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16583</v>
+        <v>14646</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-5293</v>
+        <v>-6215</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1216,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>08-APR-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,28 +1217,28 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-164</t>
+          <t>Saudia SV-312</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>12186</v>
+        <v>8431</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>16583</v>
+        <v>14646</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-4397</v>
+        <v>-6215</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -1271,30 +1262,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-608</t>
+          <t>Saudia SV-418</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5913</v>
+        <v>8431</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>14212</v>
+        <v>14646</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-8299</v>
+        <v>-6215</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1316,28 +1307,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>Air Arabia Egypt E5-415</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>5913</v>
+        <v>8678</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>14212</v>
+        <v>14646</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-8299</v>
+        <v>-5968</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -1361,28 +1352,28 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>Air Arabia Egypt E5-410</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>5913</v>
+        <v>8678</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>14212</v>
+        <v>14646</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-8299</v>
+        <v>-5968</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -1406,30 +1397,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>flynas XY-266</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>5913</v>
+        <v>10788</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>14212</v>
+        <v>14646</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-8299</v>
+        <v>-3858</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1451,30 +1442,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>flynas XY-276</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6051</v>
+        <v>10788</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>14212</v>
+        <v>14646</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-8161</v>
+        <v>-3858</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1496,30 +1487,30 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>flynas XY-268</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6051</v>
+        <v>10788</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>14212</v>
+        <v>14646</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-8161</v>
+        <v>-3858</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1541,30 +1532,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>6051</v>
+        <v>10788</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>14212</v>
+        <v>14646</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-8161</v>
+        <v>-3858</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1586,30 +1577,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>6051</v>
+        <v>10788</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>14212</v>
+        <v>14646</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-8161</v>
+        <v>-3858</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1631,30 +1622,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-276</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>6878</v>
+        <v>10788</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>14212</v>
+        <v>14646</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-7334</v>
+        <v>-3858</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1676,28 +1667,28 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>Saudia SV-310</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>6878</v>
+        <v>11170</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>14212</v>
+        <v>14646</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-7334</v>
+        <v>-3476</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -1711,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,28 +1712,28 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>6878</v>
+        <v>4194</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-7334</v>
+        <v>-8853</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -1756,7 +1747,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1757,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-164</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6906</v>
+        <v>5597</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-7306</v>
+        <v>-7450</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1792,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1802,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-160</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>6906</v>
+        <v>5597</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-7306</v>
+        <v>-7450</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1837,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,28 +1847,28 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-415</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7241</v>
+        <v>5737</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-6971</v>
+        <v>-7310</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -1891,7 +1882,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,28 +1892,28 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-410</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>7241</v>
+        <v>5737</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-6971</v>
+        <v>-7310</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -1936,7 +1927,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,28 +1937,28 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-251</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7692</v>
+        <v>5737</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-6520</v>
+        <v>-7310</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -1981,7 +1972,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1982,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>flyadeal F3-608</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>8119</v>
+        <v>6018</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-6093</v>
+        <v>-7029</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>15</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2017,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,30 +2027,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-320</t>
+          <t>Nesma Airlines NE-160</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>8174</v>
+        <v>6383</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-6038</v>
+        <v>-6664</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2062,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,28 +2072,28 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-310</t>
+          <t>flynas XY-266</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>8174</v>
+        <v>6439</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-6038</v>
+        <v>-6608</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -2116,7 +2107,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,28 +2117,28 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-312</t>
+          <t>flynas XY-276</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>8174</v>
+        <v>6439</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-6038</v>
+        <v>-6608</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -2161,7 +2152,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,28 +2162,28 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-418</t>
+          <t>flynas XY-268</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>8174</v>
+        <v>6439</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-6038</v>
+        <v>-6608</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -2206,7 +2197,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,30 +2207,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>8533</v>
+        <v>6439</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-5679</v>
+        <v>-6608</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2242,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>08-APR-26</t>
+          <t>15-APR-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,28 +2252,28 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>Air Arabia Egypt E5-415</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>9001</v>
+        <v>6841</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-5211</v>
+        <v>-6206</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -2306,28 +2297,28 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>Air Arabia Egypt E5-410</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>4535</v>
+        <v>6841</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-9677</v>
+        <v>-6206</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -2351,28 +2342,28 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>Nesma Airlines NE-164</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>4535</v>
+        <v>6986</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-9677</v>
+        <v>-6061</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -2396,28 +2387,28 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-608</t>
+          <t>Nile Air NP-251</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>4948</v>
+        <v>7210</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-9264</v>
+        <v>-5837</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>MEDIUM THREAT - MONITOR</t>
         </is>
@@ -2441,30 +2432,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>Saudia SV-320</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>4948</v>
+        <v>8431</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-9264</v>
+        <v>-4616</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2486,30 +2477,30 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>Saudia SV-310</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>5362</v>
+        <v>8431</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-8850</v>
+        <v>-4616</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2531,30 +2522,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-276</t>
+          <t>Saudia SV-312</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>5362</v>
+        <v>8431</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-8850</v>
+        <v>-4616</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2576,30 +2567,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>Saudia SV-418</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>5362</v>
+        <v>8431</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>14212</v>
+        <v>13047</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-8850</v>
+        <v>-4616</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2602,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>22-APR-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,30 +2612,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>flynas XY-266</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>5362</v>
+        <v>4194</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-8850</v>
+        <v>-6061</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>20</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2656,7 +2647,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>22-APR-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,30 +2657,30 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>flynas XY-276</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>5362</v>
+        <v>4194</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-8850</v>
+        <v>-6061</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>20</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2701,7 +2692,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>22-APR-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,30 +2702,30 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>5362</v>
+        <v>4194</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-8850</v>
+        <v>-6061</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>20</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2737,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>22-APR-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,30 +2747,30 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>5362</v>
+        <v>4194</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-8850</v>
+        <v>-6061</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>20</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2791,7 +2782,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>22-APR-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2805,26 +2796,26 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>5679</v>
+        <v>5751</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-8533</v>
+        <v>-4504</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>10</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,7 +2827,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>22-APR-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2850,26 +2841,26 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>5679</v>
+        <v>5751</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-8533</v>
+        <v>-4504</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>10</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2881,7 +2872,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>22-APR-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,30 +2882,30 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-320</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>6354</v>
+        <v>6860</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-7858</v>
+        <v>-3395</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2917,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>22-APR-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,30 +2927,30 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-310</t>
+          <t>flynas XY-268</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>6354</v>
+        <v>6860</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-7858</v>
+        <v>-3395</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2971,7 +2962,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>22-APR-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,30 +2972,30 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-418</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>6354</v>
+        <v>7814</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-7858</v>
+        <v>-2441</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>7</v>
+        <v>-6</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3016,7 +3007,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>22-APR-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,30 +3017,30 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-415</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>6726</v>
+        <v>7814</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-7486</v>
+        <v>-2441</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3061,7 +3052,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>29-APR-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,30 +3062,30 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-410</t>
+          <t>flynas XY-266</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>6726</v>
+        <v>4194</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-7486</v>
+        <v>-6061</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3106,7 +3097,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>29-APR-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,30 +3107,30 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-251</t>
+          <t>flynas XY-276</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>7692</v>
+        <v>4194</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-6520</v>
+        <v>-6061</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3151,7 +3142,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>29-APR-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,30 +3152,30 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>flynas XY-268</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>7705</v>
+        <v>4194</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-6507</v>
+        <v>-6061</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>20</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3196,7 +3187,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>29-APR-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,30 +3197,30 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>8119</v>
+        <v>4194</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-6093</v>
+        <v>-6061</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>20</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3241,7 +3232,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>29-APR-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,28 +3242,28 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-312</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>8174</v>
+        <v>4194</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-6038</v>
+        <v>-6061</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -3286,7 +3277,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15-APR-26</t>
+          <t>29-APR-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,30 +3287,30 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>8588</v>
+        <v>4194</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>14212</v>
+        <v>10255</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-5624</v>
+        <v>-6061</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>-16</v>
+        <v>20</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3331,7 +3322,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>29-APR-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,28 +3332,28 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-608</t>
+          <t>Nesma Airlines NE-164</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>4535</v>
+        <v>5751</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>11055</v>
+        <v>10255</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-6520</v>
+        <v>-4504</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -3376,7 +3367,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>29-APR-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,28 +3377,28 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>Nesma Airlines NE-160</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>4535</v>
+        <v>5751</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>11055</v>
+        <v>10255</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-6520</v>
+        <v>-4504</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -3421,7 +3412,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>29-APR-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,28 +3422,28 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>4535</v>
+        <v>6860</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>11055</v>
+        <v>10255</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-6520</v>
+        <v>-3395</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -3466,7 +3457,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>29-APR-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,28 +3467,28 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>4535</v>
+        <v>7435</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>11055</v>
+        <v>10255</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-6520</v>
+        <v>-2820</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -3511,7 +3502,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>29-APR-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,28 +3512,28 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>4811</v>
+        <v>8319</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>11055</v>
+        <v>10255</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-6244</v>
+        <v>-1936</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -3556,7 +3547,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,30 +3557,30 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>flyadeal F3-608</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>4811</v>
+        <v>6018</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>11055</v>
+        <v>14646</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-6244</v>
+        <v>-8628</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3601,7 +3592,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,30 +3602,30 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>4811</v>
+        <v>6018</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>11055</v>
+        <v>14646</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-6244</v>
+        <v>-8628</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3646,7 +3637,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,30 +3647,30 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>4811</v>
+        <v>6018</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>11055</v>
+        <v>14646</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-6244</v>
+        <v>-8628</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3691,7 +3682,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,30 +3692,30 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>Saudia SV-310</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>4811</v>
+        <v>6158</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>11055</v>
+        <v>14646</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-6244</v>
+        <v>-8488</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3736,7 +3727,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,30 +3737,30 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-276</t>
+          <t>Saudia SV-312</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>5362</v>
+        <v>6158</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>11055</v>
+        <v>14646</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-5693</v>
+        <v>-8488</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3781,7 +3772,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,30 +3782,30 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>Saudia SV-418</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>5362</v>
+        <v>6158</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>11055</v>
+        <v>14646</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-5693</v>
+        <v>-8488</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3826,7 +3817,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,28 +3827,28 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-320</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>5734</v>
+        <v>6860</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>11055</v>
+        <v>14646</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-5321</v>
+        <v>-7786</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -3871,7 +3862,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,30 +3872,30 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-310</t>
+          <t>Saudia SV-320</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>5734</v>
+        <v>8912</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>11055</v>
+        <v>14646</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-5321</v>
+        <v>-5734</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3916,7 +3907,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,30 +3917,30 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-312</t>
+          <t>Saudia SV-322</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>6354</v>
+        <v>8912</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>11055</v>
+        <v>14646</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-4701</v>
+        <v>-5734</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3961,7 +3952,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3971,28 +3962,28 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-418</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>6354</v>
+        <v>12527</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>11055</v>
+        <v>14646</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-4701</v>
+        <v>-2119</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -4006,7 +3997,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,28 +4007,28 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-415</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>6726</v>
+        <v>12527</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>11055</v>
+        <v>14646</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-4329</v>
+        <v>-2119</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -4051,7 +4042,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4061,28 +4052,28 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-410</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>6726</v>
+        <v>12527</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>11055</v>
+        <v>14646</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-4329</v>
+        <v>-2119</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -4096,7 +4087,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4106,17 +4097,17 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>7319</v>
+        <v>13425</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>11055</v>
+        <v>14646</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-3736</v>
+        <v>-1221</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>46</v>
@@ -4129,7 +4120,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4141,7 +4132,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>22-APR-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4151,30 +4142,30 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flyadeal F3-608</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>7705</v>
+        <v>5597</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>11055</v>
+        <v>11447</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-3350</v>
+        <v>-5850</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4186,7 +4177,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4196,28 +4187,28 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-160</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>4673</v>
+        <v>5597</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>9070</v>
+        <v>11447</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-4397</v>
+        <v>-5850</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -4231,7 +4222,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4241,28 +4232,28 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>4811</v>
+        <v>5597</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>9070</v>
+        <v>11447</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-4259</v>
+        <v>-5850</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -4276,7 +4267,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4286,28 +4277,28 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>Saudia SV-320</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>4811</v>
+        <v>6158</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>9070</v>
+        <v>11447</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-4259</v>
+        <v>-5289</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -4321,7 +4312,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4331,28 +4322,28 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>Saudia SV-322</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>4811</v>
+        <v>6158</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>9070</v>
+        <v>11447</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-4259</v>
+        <v>-5289</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -4366,7 +4357,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4376,28 +4367,28 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>Saudia SV-310</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>4811</v>
+        <v>6158</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>9070</v>
+        <v>11447</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-4259</v>
+        <v>-5289</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -4411,7 +4402,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,28 +4412,28 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>Saudia SV-312</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>4811</v>
+        <v>6158</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>9070</v>
+        <v>11447</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-4259</v>
+        <v>-5289</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -4456,7 +4447,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,28 +4457,28 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>Saudia SV-418</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4811</v>
+        <v>6158</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>9070</v>
+        <v>11447</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-4259</v>
+        <v>-5289</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -4501,7 +4492,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,28 +4502,28 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-310</t>
+          <t>flynas XY-268</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>5072</v>
+        <v>6158</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>9070</v>
+        <v>11447</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-3998</v>
+        <v>-5289</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -4546,7 +4537,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,28 +4547,28 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-164</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>5679</v>
+        <v>6158</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>9070</v>
+        <v>11447</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-3391</v>
+        <v>-5289</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -4591,7 +4582,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4601,28 +4592,28 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>7319</v>
+        <v>6158</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>9070</v>
+        <v>11447</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-1751</v>
+        <v>-5289</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
@@ -4636,7 +4627,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4646,33 +4637,528 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
+          <t>flynas XY-270</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>6158</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>11447</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-5289</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-649</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>6495</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>11447</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>-4952</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-415</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>6841</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>11447</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>-4606</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-410</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>6841</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>11447</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>-4606</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-272</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>11447</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>-4447</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
           <t>EgyptAir MS-647</t>
         </is>
       </c>
-      <c r="D93" s="2" t="n">
-        <v>8202</v>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>9070</v>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>-868</v>
-      </c>
-      <c r="G93" s="2" t="n">
+      <c r="D98" s="2" t="n">
+        <v>7393</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>11447</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>-4054</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-151</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>8305</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>11447</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>-3142</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-251</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>8305</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>11447</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>-3142</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-689</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>8669</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>11447</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>-2778</v>
+      </c>
+      <c r="G101" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H93" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I93" s="2" t="n">
+      <c r="H101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I101" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>9427</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>11447</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>-2020</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-266</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>9666</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>11447</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>-1781</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>17-JUN-26</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>8669</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>9455</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>-786</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -459,7 +459,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -556,7 +556,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">

--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -658,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -668,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-320</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10216</v>
+        <v>12864</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10807</v>
+        <v>15203</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-591</v>
+        <v>-2339</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -703,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -713,26 +722,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5622</v>
+        <v>13780</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12004</v>
+        <v>15203</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-6382</v>
+        <v>-1423</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -748,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -758,26 +767,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5622</v>
+        <v>13878</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12004</v>
+        <v>15203</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-6382</v>
+        <v>-1325</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -793,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -803,26 +812,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5622</v>
+        <v>12864</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12004</v>
+        <v>13611</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-6382</v>
+        <v>-747</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -838,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -848,26 +857,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-608</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6044</v>
+        <v>12864</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12004</v>
+        <v>13611</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-5960</v>
+        <v>-747</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -883,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -893,26 +902,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-410</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6980</v>
+        <v>12864</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12004</v>
+        <v>13611</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-5024</v>
+        <v>-747</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -928,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -938,17 +947,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>flynas XY-288</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7171</v>
+        <v>7904</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>12004</v>
+        <v>10807</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-4833</v>
+        <v>-2903</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -973,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -983,17 +992,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>flynas XY-288</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7171</v>
+        <v>7904</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12004</v>
+        <v>10807</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-4833</v>
+        <v>-2903</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1018,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1028,17 +1037,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7171</v>
+        <v>7904</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12004</v>
+        <v>10807</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4833</v>
+        <v>-2903</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1063,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1073,26 +1082,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7171</v>
+        <v>5622</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>12004</v>
+        <v>10807</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4833</v>
+        <v>-5185</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1108,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1118,17 +1127,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7171</v>
+        <v>7904</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12004</v>
+        <v>10807</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-4833</v>
+        <v>-2903</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1153,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1163,17 +1172,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7876</v>
+        <v>7904</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12004</v>
+        <v>10807</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4128</v>
+        <v>-2903</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1198,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1208,26 +1217,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
+        <v>7904</v>
+      </c>
+      <c r="E17" s="2" t="n">
         <v>10807</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>12004</v>
-      </c>
       <c r="F17" s="2" t="n">
-        <v>-1197</v>
+        <v>-2903</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1243,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1253,26 +1262,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-608</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5622</v>
+        <v>7904</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>12004</v>
+        <v>10807</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-6382</v>
+        <v>-2903</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1288,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1298,7 +1307,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>flyadeal F3-608</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -1333,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1343,7 +1352,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1378,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1388,7 +1397,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1423,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1433,26 +1442,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-415</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>6980</v>
+        <v>5622</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-5024</v>
+        <v>-6382</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1468,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1513,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1523,17 +1532,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>flynas XY-268</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7171</v>
+        <v>7200</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-4833</v>
+        <v>-4804</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1558,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1568,17 +1577,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7171</v>
+        <v>7200</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-4833</v>
+        <v>-4804</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>30</v>
@@ -1603,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1613,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7876</v>
+        <v>7200</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-4128</v>
+        <v>-4804</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>30</v>
@@ -1648,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1658,17 +1667,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>7876</v>
+        <v>7200</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-4128</v>
+        <v>-4804</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>30</v>
@@ -1693,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1703,26 +1712,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>7876</v>
+        <v>7791</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-4128</v>
+        <v>-4213</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -1738,7 +1747,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1748,17 +1757,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>flynas XY-266</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>7876</v>
+        <v>7904</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-4128</v>
+        <v>-4100</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>30</v>
@@ -1783,7 +1792,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1793,17 +1802,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-160</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>9060</v>
+        <v>7904</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-2944</v>
+        <v>-4100</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>30</v>
@@ -1828,7 +1837,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1838,26 +1847,26 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>10807</v>
+        <v>8130</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-1197</v>
+        <v>-3874</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -1873,7 +1882,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1883,17 +1892,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>11455</v>
+        <v>10807</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-549</v>
+        <v>-1197</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>46</v>
@@ -1918,7 +1927,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1928,26 +1937,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-608</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>6890</v>
+        <v>10807</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-5114</v>
+        <v>-1197</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1963,7 +1972,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1973,17 +1982,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>flyadeal F3-608</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>6890</v>
+        <v>5622</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-5114</v>
+        <v>-6382</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>15</v>
@@ -2008,7 +2017,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2018,17 +2027,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>6890</v>
+        <v>5622</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-5114</v>
+        <v>-6382</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>15</v>
@@ -2053,7 +2062,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2063,17 +2072,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>6890</v>
+        <v>5622</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-5114</v>
+        <v>-6382</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>15</v>
@@ -2098,7 +2107,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2108,26 +2117,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>8721</v>
+        <v>5622</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-3283</v>
+        <v>-6382</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2143,7 +2152,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2153,26 +2162,26 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>Air Arabia Egypt E5-415</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>8721</v>
+        <v>6980</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-3283</v>
+        <v>-5024</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2188,7 +2197,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2198,26 +2207,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>Air Arabia Egypt E5-410</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>8721</v>
+        <v>6980</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-3283</v>
+        <v>-5024</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -2233,7 +2242,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2243,26 +2252,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>11455</v>
+        <v>7200</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>12004</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-549</v>
+        <v>-4804</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2278,7 +2287,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2288,26 +2297,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>9003</v>
+        <v>7200</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>15203</v>
+        <v>12004</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-6200</v>
+        <v>-4804</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2323,7 +2332,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2333,26 +2342,26 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>9003</v>
+        <v>7791</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>15203</v>
+        <v>12004</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-6200</v>
+        <v>-4213</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -2368,7 +2377,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2378,26 +2387,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>flynas XY-266</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>9003</v>
+        <v>7904</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>15203</v>
+        <v>12004</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-6200</v>
+        <v>-4100</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -2413,7 +2422,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2423,17 +2432,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-164</t>
+          <t>flynas XY-268</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>9665</v>
+        <v>7904</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>15203</v>
+        <v>12004</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-5538</v>
+        <v>-4100</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>30</v>
@@ -2458,7 +2467,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2468,17 +2477,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-151</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>10074</v>
+        <v>7904</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>15203</v>
+        <v>12004</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-5129</v>
+        <v>-4100</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>30</v>
@@ -2503,7 +2512,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2513,17 +2522,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-251</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>10074</v>
+        <v>7904</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>15203</v>
+        <v>12004</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-5129</v>
+        <v>-4100</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>30</v>
@@ -2548,7 +2557,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2558,26 +2567,26 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-160</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>10370</v>
+        <v>8130</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>15203</v>
+        <v>12004</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-4833</v>
+        <v>-3874</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -2593,7 +2602,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2603,26 +2612,26 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-310</t>
+          <t>Nesma Airlines NE-160</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>10469</v>
+        <v>9060</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>15203</v>
+        <v>12004</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-4734</v>
+        <v>-2944</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -2638,7 +2647,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2648,26 +2657,26 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-418</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>10469</v>
+        <v>10807</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>15203</v>
+        <v>12004</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-4734</v>
+        <v>-1197</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -2683,7 +2692,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2693,17 +2702,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-320</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>12809</v>
+        <v>11455</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>15203</v>
+        <v>12004</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-2394</v>
+        <v>-549</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>46</v>
@@ -2728,7 +2737,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2738,26 +2747,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-312</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>12809</v>
+        <v>6467</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>15203</v>
+        <v>12004</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-2394</v>
+        <v>-5537</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -2773,7 +2782,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2783,33 +2792,1743 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>flyadeal F3-606</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>6890</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>12004</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-5114</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-614</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>6890</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>12004</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-5114</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-268</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>8750</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>12004</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-3254</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-264</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>8750</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>12004</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-3254</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-274</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>8750</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>12004</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-3254</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
           <t>flyadeal F3-608</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
-        <v>13371</v>
-      </c>
-      <c r="E52" s="2" t="n">
+      <c r="D57" s="2" t="n">
+        <v>7312</v>
+      </c>
+      <c r="E57" s="2" t="n">
         <v>15203</v>
       </c>
-      <c r="F52" s="2" t="n">
-        <v>-1832</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="F57" s="2" t="n">
+        <v>-7891</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-606</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>7312</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-7891</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-616</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>7312</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-7891</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-614</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>7312</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-7891</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-415</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>8044</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-7159</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-410</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>8310</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-6893</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-264</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>8750</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-6453</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-274</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>8750</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-6453</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-266</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>9595</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-5608</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-268</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>9595</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-5608</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-778</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>10539</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>-4664</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-164</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>11370</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>-3833</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-160</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>11370</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-3833</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-151</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>11384</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>-3819</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-272</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>11990</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>-3213</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-270</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>11990</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>-3213</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-689</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>12864</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>-2339</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>12864</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-2339</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-649</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>13456</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>-1747</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-647</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>13780</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>-1423</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>19-AUG-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-778</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>15472</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>17598</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>-2126</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-649</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>6636</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>-8567</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-151</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>7820</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>-7383</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-251</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>7820</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>-7383</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-310</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>7876</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>-7327</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-312</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>7876</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>-7327</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-320</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>8454</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>-6749</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-418</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>8454</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>-6749</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-164</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>10370</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>-4833</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-160</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>10370</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>-4833</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-647</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>11737</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>-3466</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-778</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>11808</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>-3395</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-689</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>12159</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>-3044</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>12159</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>15203</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>-3044</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4593</v>
+        <v>4546</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7932</v>
+        <v>7851</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3339</v>
+        <v>-3305</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4593</v>
+        <v>4546</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7932</v>
+        <v>7851</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3339</v>
+        <v>-3305</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -632,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-160</t>
+          <t>Nile Air NP-253</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4663</v>
+        <v>4546</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7932</v>
+        <v>7851</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3269</v>
+        <v>-3305</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,26 +677,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>Nesma Airlines NE-160</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12864</v>
+        <v>4615</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>15203</v>
+        <v>7851</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-2339</v>
+        <v>-3236</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -722,17 +722,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13780</v>
+        <v>10305</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15203</v>
+        <v>15047</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1423</v>
+        <v>-4742</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -743,9 +743,9 @@
       <c r="I6" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>13878</v>
+        <v>11226</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>15203</v>
+        <v>15047</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1325</v>
+        <v>-3821</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -788,9 +788,9 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>12864</v>
+        <v>11407</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13611</v>
+        <v>15047</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-747</v>
+        <v>-3640</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -833,9 +833,9 @@
       <c r="I8" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12864</v>
+        <v>10305</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13611</v>
+        <v>13471</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-747</v>
+        <v>-3166</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -902,17 +902,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12864</v>
+        <v>10305</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13611</v>
+        <v>13471</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-747</v>
+        <v>-3166</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,26 +947,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-288</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7904</v>
+        <v>10305</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>10807</v>
+        <v>13471</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-2903</v>
+        <v>-3166</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,26 +992,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-288</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7904</v>
+        <v>11226</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10807</v>
+        <v>13471</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-2903</v>
+        <v>-2245</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,26 +1037,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>Air Arabia Egypt E5-410</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7904</v>
+        <v>7435</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10807</v>
+        <v>11881</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-2903</v>
+        <v>-4446</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,26 +1082,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>flynas XY-288</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5622</v>
+        <v>7823</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10807</v>
+        <v>11881</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-5185</v>
+        <v>-4058</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>flynas XY-266</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7904</v>
+        <v>8660</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10807</v>
+        <v>11881</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-2903</v>
+        <v>-3221</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1162,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7904</v>
+        <v>8660</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>10807</v>
+        <v>11881</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-2903</v>
+        <v>-3221</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1207,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7904</v>
+        <v>8660</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>10807</v>
+        <v>11881</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-2903</v>
+        <v>-3221</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1252,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7904</v>
+        <v>8660</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>10807</v>
+        <v>11881</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-2903</v>
+        <v>-3221</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1297,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,26 +1307,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-608</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>5622</v>
+        <v>9329</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-6382</v>
+        <v>-2552</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1352,26 +1352,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>5622</v>
+        <v>9441</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-6382</v>
+        <v>-2440</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1397,26 +1397,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>5622</v>
+        <v>11226</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-6382</v>
+        <v>-655</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1442,26 +1442,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>flynas XY-288</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5622</v>
+        <v>7823</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-6382</v>
+        <v>-2873</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1487,26 +1487,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-410</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6980</v>
+        <v>7823</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-5024</v>
+        <v>-2873</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1532,26 +1532,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7200</v>
+        <v>9329</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-4804</v>
+        <v>-1367</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1577,26 +1577,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7200</v>
+        <v>9441</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-4804</v>
+        <v>-1255</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1622,26 +1622,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7200</v>
+        <v>9915</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-4804</v>
+        <v>-781</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1667,26 +1667,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>7200</v>
+        <v>10249</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-4804</v>
+        <v>-447</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1712,26 +1712,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>7791</v>
+        <v>5564</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-4213</v>
+        <v>-5132</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1757,26 +1757,26 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>7904</v>
+        <v>5564</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-4100</v>
+        <v>-5132</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1802,17 +1802,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>7904</v>
+        <v>7823</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-4100</v>
+        <v>-2873</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>30</v>
@@ -1837,7 +1837,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1847,26 +1847,26 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8130</v>
+        <v>7823</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-3874</v>
+        <v>-2873</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1892,26 +1892,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>10807</v>
+        <v>7823</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1197</v>
+        <v>-2873</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1937,26 +1937,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>10807</v>
+        <v>7823</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-1197</v>
+        <v>-2873</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1982,26 +1982,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-608</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5622</v>
+        <v>8172</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-6382</v>
+        <v>-2524</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2027,26 +2027,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>5622</v>
+        <v>8381</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-6382</v>
+        <v>-2315</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2072,26 +2072,26 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>5622</v>
+        <v>8381</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-6382</v>
+        <v>-2315</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2117,26 +2117,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>5622</v>
+        <v>9287</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>12004</v>
+        <v>10696</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-6382</v>
+        <v>-1409</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2162,26 +2162,26 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-415</t>
+          <t>flyadeal F3-608</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>6980</v>
+        <v>5564</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-5024</v>
+        <v>-6317</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2207,26 +2207,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-410</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>6980</v>
+        <v>5564</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-5024</v>
+        <v>-6317</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2252,26 +2252,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>7200</v>
+        <v>5564</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-4804</v>
+        <v>-6317</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2297,26 +2297,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>7200</v>
+        <v>5564</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-4804</v>
+        <v>-6317</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2342,26 +2342,26 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>Air Arabia Egypt E5-410</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>7791</v>
+        <v>6908</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-4213</v>
+        <v>-4973</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2387,17 +2387,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>flynas XY-268</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>7904</v>
+        <v>7126</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-4100</v>
+        <v>-4755</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>30</v>
@@ -2422,7 +2422,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2432,17 +2432,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>7904</v>
+        <v>7126</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-4100</v>
+        <v>-4755</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>30</v>
@@ -2467,7 +2467,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>7904</v>
+        <v>7126</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-4100</v>
+        <v>-4755</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>30</v>
@@ -2512,7 +2512,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>7904</v>
+        <v>7126</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-4100</v>
+        <v>-4755</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>30</v>
@@ -2557,7 +2557,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2567,17 +2567,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>8130</v>
+        <v>7377</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-3874</v>
+        <v>-4504</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>23</v>
@@ -2602,7 +2602,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2612,30 +2612,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-160</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>9060</v>
+        <v>7586</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-2944</v>
+        <v>-4295</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2657,17 +2657,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>10807</v>
+        <v>7586</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-1197</v>
+        <v>-4295</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>46</v>
@@ -2678,9 +2678,9 @@
       <c r="I49" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2702,26 +2702,26 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>11455</v>
+        <v>7711</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-549</v>
+        <v>-4170</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2747,26 +2747,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>flynas XY-266</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>6467</v>
+        <v>7823</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-5537</v>
+        <v>-4058</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2792,26 +2792,26 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>6890</v>
+        <v>7823</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>12004</v>
+        <v>11881</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-5114</v>
+        <v>-4058</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2837,17 +2837,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>flyadeal F3-608</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>6890</v>
+        <v>5564</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>12004</v>
+        <v>13471</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-5114</v>
+        <v>-7907</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>15</v>
@@ -2858,9 +2858,9 @@
       <c r="I53" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2872,7 +2872,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2882,30 +2882,30 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>8750</v>
+        <v>5564</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>12004</v>
+        <v>13471</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-3254</v>
+        <v>-7907</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2927,30 +2927,30 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>8750</v>
+        <v>5564</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>12004</v>
+        <v>13471</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-3254</v>
+        <v>-7907</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2962,7 +2962,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2972,30 +2972,30 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>8750</v>
+        <v>5564</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>12004</v>
+        <v>13471</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-3254</v>
+        <v>-7907</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3007,7 +3007,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3017,30 +3017,30 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-608</t>
+          <t>Air Arabia Egypt E5-415</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>7312</v>
+        <v>6908</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-7891</v>
+        <v>-6563</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3062,30 +3062,30 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>Air Arabia Egypt E5-410</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>7312</v>
+        <v>6908</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-7891</v>
+        <v>-6563</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3107,26 +3107,26 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>7312</v>
+        <v>7126</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-7891</v>
+        <v>-6345</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3152,26 +3152,26 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>7312</v>
+        <v>7126</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-7891</v>
+        <v>-6345</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3197,30 +3197,30 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-415</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>8044</v>
+        <v>7377</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-7159</v>
+        <v>-6094</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3242,30 +3242,30 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-410</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>8310</v>
+        <v>7586</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-6893</v>
+        <v>-5885</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3277,7 +3277,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3287,30 +3287,30 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>8750</v>
+        <v>7711</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-6453</v>
+        <v>-5760</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3332,17 +3332,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>flynas XY-266</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>8750</v>
+        <v>7823</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-6453</v>
+        <v>-5648</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>30</v>
@@ -3367,7 +3367,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3377,17 +3377,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>flynas XY-268</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>9595</v>
+        <v>7823</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-5608</v>
+        <v>-5648</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>30</v>
@@ -3398,9 +3398,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>9595</v>
+        <v>7823</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-5608</v>
+        <v>-5648</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>30</v>
@@ -3443,9 +3443,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3467,30 +3467,30 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-778</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>10539</v>
+        <v>7823</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-4664</v>
+        <v>-5648</v>
       </c>
       <c r="G67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H67" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3512,30 +3512,30 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-164</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>11370</v>
+        <v>8381</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-3833</v>
+        <v>-5090</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3561,13 +3561,13 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>11370</v>
+        <v>8966</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-3833</v>
+        <v>-4505</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>30</v>
@@ -3592,7 +3592,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3606,13 +3606,13 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>11384</v>
+        <v>9524</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-3819</v>
+        <v>-3947</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>30</v>
@@ -3637,7 +3637,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>Nile Air NP-251</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>11990</v>
+        <v>9524</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-3213</v>
+        <v>-3947</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>30</v>
@@ -3682,7 +3682,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3692,17 +3692,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>Nesma Airlines NE-164</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>11990</v>
+        <v>9566</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>15203</v>
+        <v>13471</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-3213</v>
+        <v>-3905</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>30</v>
@@ -3727,7 +3727,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3737,26 +3737,26 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>12864</v>
+        <v>6400</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>15203</v>
+        <v>11881</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-2339</v>
+        <v>-5481</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3782,26 +3782,26 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>12864</v>
+        <v>6819</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>15203</v>
+        <v>11881</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-2339</v>
+        <v>-5062</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3827,26 +3827,26 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>13456</v>
+        <v>6819</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>15203</v>
+        <v>11881</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-1747</v>
+        <v>-5062</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3872,26 +3872,26 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>flynas XY-268</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>13780</v>
+        <v>8660</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>15203</v>
+        <v>11881</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-1423</v>
+        <v>-3221</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3917,26 +3917,26 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-778</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>15472</v>
+        <v>8660</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>17598</v>
+        <v>11881</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-2126</v>
+        <v>-3221</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3962,30 +3962,30 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>6636</v>
+        <v>8660</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>15203</v>
+        <v>11881</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-8567</v>
+        <v>-3221</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4007,30 +4007,30 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-151</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>7820</v>
+        <v>8966</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>15203</v>
+        <v>11881</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-7383</v>
+        <v>-2915</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4052,30 +4052,30 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-251</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>7820</v>
+        <v>9287</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>15203</v>
+        <v>11881</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-7383</v>
+        <v>-2594</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4097,30 +4097,30 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-310</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>7876</v>
+        <v>9329</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>15203</v>
+        <v>11881</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-7327</v>
+        <v>-2552</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4142,30 +4142,30 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-312</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>7876</v>
+        <v>9329</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>15203</v>
+        <v>11881</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-7327</v>
+        <v>-2552</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4187,30 +4187,30 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-320</t>
+          <t>flyadeal F3-608</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>8454</v>
+        <v>7237</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>15203</v>
+        <v>15047</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-6749</v>
+        <v>-7810</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4222,7 +4222,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4232,30 +4232,30 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-418</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>8454</v>
+        <v>7237</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>15203</v>
+        <v>15047</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-6749</v>
+        <v>-7810</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4267,7 +4267,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4277,26 +4277,26 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-164</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>10370</v>
+        <v>7237</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>15203</v>
+        <v>15047</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-4833</v>
+        <v>-7810</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4322,26 +4322,26 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-160</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>10370</v>
+        <v>7237</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>15203</v>
+        <v>15047</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-4833</v>
+        <v>-7810</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4367,30 +4367,30 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>Air Arabia Egypt E5-415</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>11737</v>
+        <v>7961</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>15203</v>
+        <v>15047</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-3466</v>
+        <v>-7086</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4412,17 +4412,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-778</t>
+          <t>Air Arabia Egypt E5-410</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>11808</v>
+        <v>8225</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>15203</v>
+        <v>15047</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-3395</v>
+        <v>-6822</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>20</v>
@@ -4447,7 +4447,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4457,30 +4457,30 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>12159</v>
+        <v>8660</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>15203</v>
+        <v>15047</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-3044</v>
+        <v>-6387</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4502,33 +4502,1428 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
+          <t>flynas XY-266</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>9496</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>-5551</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-268</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>9496</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>-5551</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-264</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>9496</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>-5551</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-689</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>10305</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-4742</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
           <t>EgyptAir MS-651</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>15203</v>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>-3044</v>
-      </c>
-      <c r="G90" s="2" t="n">
+      <c r="D94" s="2" t="n">
+        <v>10305</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>-4742</v>
+      </c>
+      <c r="G94" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H90" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I90" s="2" t="n">
+      <c r="H94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I94" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-649</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>10891</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>-4156</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-647</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>11226</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>-3821</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-164</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>11253</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>-3794</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-160</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>11253</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>-3794</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-151</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>11267</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>-3780</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-778</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>11687</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>-3360</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-272</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>11867</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>-3180</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-270</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>11867</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>-3180</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-608</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>8911</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>-6136</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-606</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>8911</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>-6136</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-616</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>8911</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>-6136</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-614</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>8911</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>-6136</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-151</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>9970</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>-5077</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-251</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>9970</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>-5077</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-164</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>10263</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>-4784</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-160</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>10263</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>-4784</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-320</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>10361</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>-4686</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-310</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>10361</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>-4686</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-312</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>10361</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>-4686</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-418</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>10361</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>-4686</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-268</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>10473</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>-4574</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-272</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>10473</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>-4574</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-274</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>10473</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>-4574</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-270</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>10473</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>-4574</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-266</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>11867</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>-3180</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-264</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>11867</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>15047</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>-3180</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>30-SEP-26</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>7586</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>9901</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>-2315</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -468,7 +468,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -542,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-151</t>
+          <t>Nesma Airlines NE-164</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4546</v>
+        <v>3597</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7851</v>
+        <v>7837</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3305</v>
+        <v>-4240</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -587,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-251</t>
+          <t>Nesma Airlines NE-160</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4546</v>
+        <v>3597</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7851</v>
+        <v>7837</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3305</v>
+        <v>-4240</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -610,7 +610,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-253</t>
+          <t>Nile Air NP-151</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4546</v>
+        <v>3611</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7851</v>
+        <v>7837</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3305</v>
+        <v>-4226</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -655,7 +655,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-160</t>
+          <t>Nile Air NP-253</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4615</v>
+        <v>3611</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7851</v>
+        <v>7837</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-3236</v>
+        <v>-4226</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -700,7 +700,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,30 +722,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>Nile Air NP-251</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10305</v>
+        <v>3611</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15047</v>
+        <v>7837</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4742</v>
+        <v>-4226</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,30 +767,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>Nesma Airlines NE-164</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>11226</v>
+        <v>3597</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>15047</v>
+        <v>7809</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-3821</v>
+        <v>-4212</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,30 +812,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>Nesma Airlines NE-160</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>11407</v>
+        <v>3597</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>15047</v>
+        <v>7809</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-3640</v>
+        <v>-4212</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,30 +857,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>Nile Air NP-151</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10305</v>
+        <v>3611</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13471</v>
+        <v>7809</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-3166</v>
+        <v>-4198</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,30 +902,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>Nile Air NP-253</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10305</v>
+        <v>3611</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13471</v>
+        <v>7809</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-3166</v>
+        <v>-4198</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,30 +947,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>Nile Air NP-251</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10305</v>
+        <v>3611</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13471</v>
+        <v>7809</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-3166</v>
+        <v>-4198</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,30 +992,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>flynas XY-266</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>11226</v>
+        <v>8660</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13471</v>
+        <v>11853</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-2245</v>
+        <v>-3193</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1037,30 +1037,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-410</t>
+          <t>flynas XY-288</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7435</v>
+        <v>8660</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4446</v>
+        <v>-3193</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-288</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7823</v>
+        <v>8660</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4058</v>
+        <v>-3193</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
         <v>8660</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3221</v>
+        <v>-3193</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>8660</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-3221</v>
+        <v>-3193</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1217,30 +1217,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8660</v>
+        <v>9301</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-3221</v>
+        <v>-2552</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1262,30 +1262,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8660</v>
+        <v>9413</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-3221</v>
+        <v>-2440</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>9329</v>
+        <v>10208</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-2552</v>
+        <v>-1645</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1352,30 +1352,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>Air Arabia Egypt E5-415</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9441</v>
+        <v>7102</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-2440</v>
+        <v>-4751</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1397,30 +1397,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>Air Arabia Egypt E5-410</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>11226</v>
+        <v>7102</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-655</v>
+        <v>-4751</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-288</t>
+          <t>flynas XY-266</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7823</v>
+        <v>8660</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>10696</v>
+        <v>11853</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-2873</v>
+        <v>-3193</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1487,17 +1487,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>flynas XY-288</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>7823</v>
+        <v>8660</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>10696</v>
+        <v>11853</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-2873</v>
+        <v>-3193</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1532,30 +1532,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>9329</v>
+        <v>8660</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10696</v>
+        <v>11853</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-1367</v>
+        <v>-3193</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1577,30 +1577,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>9441</v>
+        <v>8660</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>10696</v>
+        <v>11853</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-1255</v>
+        <v>-3193</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>9915</v>
+        <v>9301</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>10696</v>
+        <v>11853</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-781</v>
+        <v>-2552</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46</v>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1667,17 +1667,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>10249</v>
+        <v>9413</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>10696</v>
+        <v>11853</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-447</v>
+        <v>-2440</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>46</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1712,30 +1712,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>5564</v>
+        <v>9887</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>10696</v>
+        <v>11853</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-5132</v>
+        <v>-1966</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1757,30 +1757,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>5564</v>
+        <v>10208</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>10696</v>
+        <v>11853</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-5132</v>
+        <v>-1645</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1802,30 +1802,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>7823</v>
+        <v>5564</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>10696</v>
+        <v>10668</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-2873</v>
+        <v>-5104</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1847,30 +1847,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>flyadeal F3-614</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>7823</v>
+        <v>5564</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>10696</v>
+        <v>10668</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-2873</v>
+        <v>-5104</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1892,30 +1892,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>7823</v>
+        <v>5982</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>10696</v>
+        <v>10668</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-2873</v>
+        <v>-4686</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1937,30 +1937,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7823</v>
+        <v>5982</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>10696</v>
+        <v>10668</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-2873</v>
+        <v>-4686</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1982,30 +1982,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>8172</v>
+        <v>7823</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>10696</v>
+        <v>10668</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-2524</v>
+        <v>-2845</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2027,30 +2027,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>8381</v>
+        <v>7823</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>10696</v>
+        <v>10668</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-2315</v>
+        <v>-2845</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2072,30 +2072,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>8381</v>
+        <v>7823</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>10696</v>
+        <v>10668</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-2315</v>
+        <v>-2845</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>9287</v>
+        <v>8158</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>10696</v>
+        <v>10668</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-1409</v>
+        <v>-2510</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>46</v>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2162,30 +2162,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-608</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>5564</v>
+        <v>10235</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>11881</v>
+        <v>10668</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-6317</v>
+        <v>-433</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2207,17 +2207,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>flyadeal F3-608</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
         <v>5564</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-6317</v>
+        <v>-6289</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>15</v>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
         <v>5564</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-6317</v>
+        <v>-6289</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>15</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2304,10 +2304,10 @@
         <v>5564</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-6317</v>
+        <v>-6289</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>15</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2342,30 +2342,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-410</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>6908</v>
+        <v>6400</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-4973</v>
+        <v>-5453</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2387,30 +2387,30 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>7126</v>
+        <v>6791</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-4755</v>
+        <v>-5062</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2432,30 +2432,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>7126</v>
+        <v>6791</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-4755</v>
+        <v>-5062</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2477,30 +2477,30 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>Air Arabia Egypt E5-410</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>7126</v>
+        <v>6841</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-4755</v>
+        <v>-5012</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>flynas XY-268</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
         <v>7126</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-4755</v>
+        <v>-4727</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>30</v>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2567,30 +2567,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7377</v>
+        <v>7126</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-4504</v>
+        <v>-4727</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2612,30 +2612,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>7586</v>
+        <v>7126</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-4295</v>
+        <v>-4727</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2657,30 +2657,30 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>7586</v>
+        <v>7126</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-4295</v>
+        <v>-4727</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2702,17 +2702,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>7711</v>
+        <v>7377</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-4170</v>
+        <v>-4476</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>23</v>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2747,30 +2747,30 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>7823</v>
+        <v>7683</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-4058</v>
+        <v>-4170</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2792,17 +2792,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>flynas XY-266</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
         <v>7823</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>11881</v>
+        <v>11853</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-4058</v>
+        <v>-4030</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>30</v>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2837,30 +2837,30 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-608</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>5564</v>
+        <v>7823</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>13471</v>
+        <v>11853</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-7907</v>
+        <v>-4030</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2872,7 +2872,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2882,17 +2882,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>flyadeal F3-616</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>5564</v>
+        <v>6400</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>13471</v>
+        <v>11853</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-7907</v>
+        <v>-5453</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>15</v>
@@ -2903,9 +2903,9 @@
       <c r="I54" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2927,30 +2927,30 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>5564</v>
+        <v>6791</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>13471</v>
+        <v>11853</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-7907</v>
+        <v>-5062</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2962,7 +2962,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2972,30 +2972,30 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>5564</v>
+        <v>7572</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>13471</v>
+        <v>11853</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-7907</v>
+        <v>-4281</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3007,7 +3007,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3017,30 +3017,30 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-415</t>
+          <t>flynas XY-268</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>6908</v>
+        <v>8660</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>13471</v>
+        <v>11853</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-6563</v>
+        <v>-3193</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3062,30 +3062,30 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-410</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>6908</v>
+        <v>8660</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>13471</v>
+        <v>11853</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-6563</v>
+        <v>-3193</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3107,17 +3107,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>flynas XY-274</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>7126</v>
+        <v>8660</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>13471</v>
+        <v>11853</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-6345</v>
+        <v>-3193</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>30</v>
@@ -3128,9 +3128,9 @@
       <c r="I59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3152,30 +3152,30 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-274</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>7126</v>
+        <v>8939</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>13471</v>
+        <v>11853</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-6345</v>
+        <v>-2914</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3197,30 +3197,30 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>7377</v>
+        <v>9259</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>13471</v>
+        <v>11853</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-6094</v>
+        <v>-2594</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3246,26 +3246,26 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>7586</v>
+        <v>6791</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>13471</v>
+        <v>15005</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-5885</v>
+        <v>-8214</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3277,7 +3277,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3291,13 +3291,13 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>7711</v>
+        <v>7697</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>13471</v>
+        <v>15005</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-5760</v>
+        <v>-7308</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>23</v>
@@ -3308,9 +3308,9 @@
       <c r="I63" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3332,30 +3332,30 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>7823</v>
+        <v>10291</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>13471</v>
+        <v>15005</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-5648</v>
+        <v>-4714</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3377,30 +3377,30 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>flyadeal F3-778</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>7823</v>
+        <v>10431</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>13471</v>
+        <v>15005</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-5648</v>
+        <v>-4574</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>30</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3422,30 +3422,30 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>7823</v>
+        <v>10877</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>13471</v>
+        <v>15005</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-5648</v>
+        <v>-4128</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3467,17 +3467,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>Nesma Airlines NE-160</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>7823</v>
+        <v>11212</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>13471</v>
+        <v>15005</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-5648</v>
+        <v>-3793</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>30</v>
@@ -3488,9 +3488,9 @@
       <c r="I67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3512,30 +3512,30 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>Nile Air NP-151</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>8381</v>
+        <v>11240</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>13471</v>
+        <v>15005</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-5090</v>
+        <v>-3765</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3557,17 +3557,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-160</t>
+          <t>Nile Air NP-151</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>8966</v>
+        <v>9943</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>13471</v>
+        <v>15005</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-4505</v>
+        <v>-5062</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>30</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3592,7 +3592,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3602,17 +3602,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-151</t>
+          <t>Nile Air NP-251</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>9524</v>
+        <v>9943</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>13471</v>
+        <v>15005</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-3947</v>
+        <v>-5062</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>30</v>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-251</t>
+          <t>Nesma Airlines NE-164</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>9524</v>
+        <v>10194</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>13471</v>
+        <v>15005</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-3947</v>
+        <v>-4811</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>30</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3682,7 +3682,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3692,17 +3692,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-164</t>
+          <t>Nesma Airlines NE-160</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>9566</v>
+        <v>10194</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>13471</v>
+        <v>15005</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-3905</v>
+        <v>-4811</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>30</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3737,30 +3737,30 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-616</t>
+          <t>Saudia SV-320</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>6400</v>
+        <v>10668</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>11881</v>
+        <v>15005</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-5481</v>
+        <v>-4337</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3772,7 +3772,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3782,30 +3782,30 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>Saudia SV-310</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>6819</v>
+        <v>10668</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>11881</v>
+        <v>15005</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-5062</v>
+        <v>-4337</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3827,30 +3827,30 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-614</t>
+          <t>Saudia SV-312</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>6819</v>
+        <v>10668</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>11881</v>
+        <v>15005</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-5062</v>
+        <v>-4337</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3872,2058 +3872,33 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>Saudia SV-418</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>8660</v>
+        <v>10668</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>11881</v>
+        <v>15005</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-3221</v>
+        <v>-4337</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-264</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="n">
-        <v>8660</v>
-      </c>
-      <c r="E77" s="2" t="n">
-        <v>11881</v>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>-3221</v>
-      </c>
-      <c r="G77" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-274</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>8660</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>11881</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>-3221</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-649</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="n">
-        <v>8966</v>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>11881</v>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>-2915</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-647</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="n">
-        <v>9287</v>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>11881</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>-2594</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-689</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="n">
-        <v>9329</v>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>11881</v>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>-2552</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-651</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>9329</v>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>11881</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>-2552</v>
-      </c>
-      <c r="G82" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-608</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>7237</v>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>-7810</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-606</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>7237</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>-7810</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-616</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>7237</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>-7810</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-614</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="n">
-        <v>7237</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>-7810</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-415</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>7961</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>-7086</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-410</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>8225</v>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>-6822</v>
-      </c>
-      <c r="G88" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-274</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>8660</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>-6387</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-266</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>9496</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>-5551</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-268</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>9496</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F91" s="2" t="n">
-        <v>-5551</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-264</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="n">
-        <v>9496</v>
-      </c>
-      <c r="E92" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>-5551</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-689</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="n">
-        <v>10305</v>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>-4742</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-651</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="n">
-        <v>10305</v>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>-4742</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-649</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="n">
-        <v>10891</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>-4156</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-647</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>11226</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>-3821</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-164</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="n">
-        <v>11253</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>-3794</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-160</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>11253</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F98" s="2" t="n">
-        <v>-3794</v>
-      </c>
-      <c r="G98" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-151</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>11267</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>-3780</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-778</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>11687</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>-3360</v>
-      </c>
-      <c r="G100" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-272</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>11867</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>-3180</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-270</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>11867</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>-3180</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-608</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>8911</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>-6136</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-606</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="n">
-        <v>8911</v>
-      </c>
-      <c r="E104" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F104" s="2" t="n">
-        <v>-6136</v>
-      </c>
-      <c r="G104" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-616</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="n">
-        <v>8911</v>
-      </c>
-      <c r="E105" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>-6136</v>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-614</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>8911</v>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>-6136</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-151</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>9970</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F107" s="2" t="n">
-        <v>-5077</v>
-      </c>
-      <c r="G107" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-251</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="n">
-        <v>9970</v>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>-5077</v>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-164</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="n">
-        <v>10263</v>
-      </c>
-      <c r="E109" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>-4784</v>
-      </c>
-      <c r="G109" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-160</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="n">
-        <v>10263</v>
-      </c>
-      <c r="E110" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>-4784</v>
-      </c>
-      <c r="G110" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-320</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="n">
-        <v>10361</v>
-      </c>
-      <c r="E111" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>-4686</v>
-      </c>
-      <c r="G111" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I111" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K111" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-310</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="n">
-        <v>10361</v>
-      </c>
-      <c r="E112" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F112" s="2" t="n">
-        <v>-4686</v>
-      </c>
-      <c r="G112" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I112" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-312</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="n">
-        <v>10361</v>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>-4686</v>
-      </c>
-      <c r="G113" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I113" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-418</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="n">
-        <v>10361</v>
-      </c>
-      <c r="E114" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>-4686</v>
-      </c>
-      <c r="G114" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H114" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I114" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-268</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>10473</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>-4574</v>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-272</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>10473</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>-4574</v>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-274</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>10473</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>-4574</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K117" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-270</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>10473</v>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>-4574</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-266</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="n">
-        <v>11867</v>
-      </c>
-      <c r="E119" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>-3180</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K119" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-264</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="n">
-        <v>11867</v>
-      </c>
-      <c r="E120" s="2" t="n">
-        <v>15047</v>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>-3180</v>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>30-SEP-26</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-651</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>7586</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>9901</v>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>-2315</v>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K121" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,9 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -799,276 +790,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>09-JUN-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-689</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>9456</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>12018</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-2562</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>09-JUN-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-651</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>9569</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>12018</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-2449</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>09-JUN-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-647</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>10376</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>12018</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-1642</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-689</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>9456</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>13617</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-4161</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-651</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>9569</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>13617</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-4048</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-649</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>10050</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>13617</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-3567</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +92,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -537,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3638</v>
+        <v>3621</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7941</v>
+        <v>7920</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4303</v>
+        <v>-4299</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -582,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3638</v>
+        <v>3621</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7941</v>
+        <v>7920</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4303</v>
+        <v>-4299</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -627,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3638</v>
+        <v>3621</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7941</v>
+        <v>7920</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4303</v>
+        <v>-4299</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -672,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>11834</v>
+        <v>11809</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13617</v>
+        <v>13599</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1783</v>
+        <v>-1790</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -717,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12372</v>
+        <v>12359</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13617</v>
+        <v>13599</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1245</v>
+        <v>-1240</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -762,13 +780,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12372</v>
+        <v>12359</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13617</v>
+        <v>13599</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1245</v>
+        <v>-1240</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -785,6 +803,1266 @@
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>09-JUN-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>9540</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>13599</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-4059</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>09-JUN-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-647</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>10358</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>13599</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-3241</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>09-JUN-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-689</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>10414</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>13599</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-3185</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-689</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>9427</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>13599</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-4172</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>9540</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>13599</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-4059</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-647</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>10358</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>13599</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-3241</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>16-JUN-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-689</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>9427</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-578</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>16-JUN-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>9540</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-465</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>17-JUN-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-689</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>9427</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-578</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>17-JUN-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>9427</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-578</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>21-JUL-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-270</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>5763</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>12006</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-6243</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>21-JUL-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>6863</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>12006</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-5143</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>21-JUL-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-689</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>7666</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>12006</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-4340</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-689</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>6863</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>13599</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-6736</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>7666</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>13599</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-5933</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-647</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>8582</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>13599</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-5017</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>8455</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>12006</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-3551</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-649</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>9047</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>12006</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-2959</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-647</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>9385</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>12006</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-2621</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>8455</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>15191</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-6736</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-689</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>9427</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>15191</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-5764</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-649</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>11006</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>15191</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-4185</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-778</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>12092</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>15191</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-3099</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-647</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>8582</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>15191</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-6609</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-689</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>9427</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>15191</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-5764</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>9427</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>15191</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-5764</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>30-SEP-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>7666</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-2339</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>30-SEP-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-647</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>8582</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-1423</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,12 +58,6 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -558,10 +549,10 @@
         <v>3621</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7920</v>
+        <v>7934</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4299</v>
+        <v>-4313</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -603,10 +594,10 @@
         <v>3621</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7920</v>
+        <v>7934</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4299</v>
+        <v>-4313</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -648,10 +639,10 @@
         <v>3621</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7920</v>
+        <v>7934</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4299</v>
+        <v>-4313</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -690,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>11809</v>
+        <v>11823</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>13599</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1790</v>
+        <v>-1776</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -956,17 +947,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9427</v>
+        <v>9540</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>13599</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-4172</v>
+        <v>-4059</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -1001,17 +992,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9540</v>
+        <v>10019</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>13599</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-4059</v>
+        <v>-3580</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1098,10 +1089,10 @@
         <v>9427</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10005</v>
+        <v>10809</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-578</v>
+        <v>-1382</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1143,10 +1134,10 @@
         <v>9540</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10005</v>
+        <v>10809</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-465</v>
+        <v>-1269</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1171,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1172,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9427</v>
+        <v>10019</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>10005</v>
+        <v>10809</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-578</v>
+        <v>-790</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1226,7 +1217,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
@@ -1261,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1262,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5763</v>
+        <v>9427</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>12006</v>
+        <v>10005</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-6243</v>
+        <v>-578</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1320,22 +1311,22 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6863</v>
+        <v>7666</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>12006</v>
+        <v>10809</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-5143</v>
+        <v>-3143</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1351,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1352,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>7666</v>
+        <v>8258</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>12006</v>
+        <v>10809</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-4340</v>
+        <v>-2551</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1382,9 +1373,9 @@
       <c r="I20" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1410,26 +1401,26 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6863</v>
+        <v>8469</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>13599</v>
+        <v>10809</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-6736</v>
+        <v>-2340</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,30 +1442,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7666</v>
+        <v>5763</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>13599</v>
+        <v>12006</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-5933</v>
+        <v>-6243</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,30 +1487,30 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8582</v>
+        <v>6863</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>13599</v>
+        <v>12006</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-5017</v>
+        <v>-5143</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1545,26 +1536,26 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>8455</v>
+        <v>6863</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>12006</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-3551</v>
+        <v>-5143</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,17 +1577,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>9047</v>
+        <v>7666</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>12006</v>
+        <v>13599</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-2959</v>
+        <v>-5933</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46</v>
@@ -1607,9 +1598,9 @@
       <c r="I25" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1635,13 +1626,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>9385</v>
+        <v>8582</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>12006</v>
+        <v>13599</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-2621</v>
+        <v>-5017</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46</v>
@@ -1652,9 +1643,9 @@
       <c r="I26" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1667,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flynas XY-266</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>8455</v>
+        <v>9202</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>15191</v>
+        <v>13599</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-6736</v>
+        <v>-4397</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,30 +1712,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>flyadeal F3-778</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>9427</v>
+        <v>12092</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>15191</v>
+        <v>13599</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-5764</v>
+        <v>-1507</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1747,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,17 +1757,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>11006</v>
+        <v>8469</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>15191</v>
+        <v>12006</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-4185</v>
+        <v>-3537</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>46</v>
@@ -1801,7 +1792,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,26 +1802,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-778</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>12092</v>
+        <v>9061</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>15191</v>
+        <v>12006</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-3099</v>
+        <v>-2945</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1846,7 +1837,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1860,13 +1851,13 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8582</v>
+        <v>9385</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>15191</v>
+        <v>12006</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-6609</v>
+        <v>-2621</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>46</v>
@@ -1877,9 +1868,9 @@
       <c r="I31" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1882,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,30 +1892,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>flyadeal F3-778</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>9427</v>
+        <v>15756</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>15191</v>
+        <v>17601</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-5764</v>
+        <v>-1845</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1927,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>30-SEP-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1950,13 +1941,13 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>9427</v>
+        <v>7666</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>15191</v>
+        <v>10005</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-5764</v>
+        <v>-2339</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>46</v>
@@ -1967,9 +1958,9 @@
       <c r="I33" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1991,17 +1982,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7666</v>
+        <v>8582</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>10005</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-2339</v>
+        <v>-1423</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>46</v>
@@ -2018,51 +2009,6 @@
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>30-SEP-26</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-647</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>8582</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>10005</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>-1423</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -857,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10358</v>
+        <v>10414</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>13599</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-3241</v>
+        <v>-3185</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -878,9 +887,9 @@
       <c r="I9" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -902,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10414</v>
+        <v>11344</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>13599</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-3185</v>
+        <v>-2255</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -1442,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>flynas XY-266</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5763</v>
+        <v>9202</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>12006</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-6243</v>
+        <v>-2804</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1487,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>flynas XY-268</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6863</v>
+        <v>9202</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>12006</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-5143</v>
+        <v>-2804</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1532,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>6863</v>
+        <v>9202</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>12006</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-5143</v>
+        <v>-2804</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1577,26 +1586,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7666</v>
+        <v>6863</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>13599</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-5933</v>
+        <v>-6736</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -1622,17 +1631,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>8582</v>
+        <v>7666</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>13599</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-5017</v>
+        <v>-5933</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46</v>
@@ -1667,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>9202</v>
+        <v>8582</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>13599</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-4397</v>
+        <v>-5017</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -1882,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1892,30 +1901,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-778</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>15756</v>
+        <v>8469</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>17601</v>
+        <v>15205</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1845</v>
+        <v>-6736</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1927,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30-SEP-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1937,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7666</v>
+        <v>9427</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>10005</v>
+        <v>15205</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-2339</v>
+        <v>-5778</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>46</v>
@@ -1958,9 +1967,9 @@
       <c r="I33" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1972,43 +1981,538 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-264</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>10048</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>15205</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-5157</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-778</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>12092</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>15205</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-3113</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>12-AUG-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-778</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>15756</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>17601</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-1845</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>19-AUG-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-778</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>15756</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>17601</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-1845</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-151</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>10076</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>15205</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-5129</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-251</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>10076</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>15205</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-5129</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-164</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>10358</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>15205</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-4847</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-647</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>8582</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>15205</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-6623</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-689</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>9427</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>15205</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-5778</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>9427</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>15205</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-5778</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>30-SEP-26</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>7666</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>10005</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-2339</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>30-SEP-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>EgyptAir MS-647</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D45" s="2" t="n">
         <v>8582</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E45" s="2" t="n">
         <v>10005</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F45" s="2" t="n">
         <v>-1423</v>
       </c>
-      <c r="G34" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="G45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10414</v>
+        <v>10358</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>13599</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-3185</v>
+        <v>-3241</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -887,9 +887,9 @@
       <c r="I9" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>11344</v>
+        <v>10414</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>13599</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-2255</v>
+        <v>-3185</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -963,10 +963,10 @@
         <v>9540</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13599</v>
+        <v>12006</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-4059</v>
+        <v>-2466</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -977,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10019</v>
+        <v>10358</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13599</v>
+        <v>12006</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-3580</v>
+        <v>-1648</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10358</v>
+        <v>10414</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13599</v>
+        <v>12006</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-3241</v>
+        <v>-1592</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>46</v>
@@ -1067,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9427</v>
+        <v>9540</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10809</v>
+        <v>13599</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-1382</v>
+        <v>-4059</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1112,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9540</v>
+        <v>10019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10809</v>
+        <v>13599</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-1269</v>
+        <v>-3580</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>10019</v>
+        <v>10358</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>10809</v>
+        <v>13599</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-790</v>
+        <v>-3241</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1202,9 +1202,9 @@
       <c r="I16" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1233,10 +1233,10 @@
         <v>9427</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>10005</v>
+        <v>10809</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-578</v>
+        <v>-1382</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>9427</v>
+        <v>9540</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>10005</v>
+        <v>10809</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-578</v>
+        <v>-1269</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>46</v>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>7666</v>
+        <v>10019</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>10809</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-3143</v>
+        <v>-790</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8258</v>
+        <v>9427</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>10809</v>
+        <v>10005</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-2551</v>
+        <v>-578</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8469</v>
+        <v>9427</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>10809</v>
+        <v>10005</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-2340</v>
+        <v>-578</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-266</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>9202</v>
+        <v>7666</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>12006</v>
+        <v>10809</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-2804</v>
+        <v>-3143</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-268</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9202</v>
+        <v>8258</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>12006</v>
+        <v>10809</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-2804</v>
+        <v>-2551</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>9202</v>
+        <v>8469</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>12006</v>
+        <v>10809</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-2804</v>
+        <v>-2340</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1593,10 +1593,10 @@
         <v>6863</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>13599</v>
+        <v>12006</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-6736</v>
+        <v>-5143</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>23</v>
@@ -1607,9 +1607,9 @@
       <c r="I25" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1635,26 +1635,26 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7666</v>
+        <v>6863</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>13599</v>
+        <v>12006</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-5933</v>
+        <v>-5143</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>flynas XY-272</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>8582</v>
+        <v>9202</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>13599</v>
+        <v>12006</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-5017</v>
+        <v>-2804</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-778</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>12092</v>
+        <v>6863</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>13599</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-1507</v>
+        <v>-6736</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>8469</v>
+        <v>7666</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>12006</v>
+        <v>13599</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-3537</v>
+        <v>-5933</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>46</v>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>9061</v>
+        <v>8582</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>12006</v>
+        <v>13599</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-2945</v>
+        <v>-5017</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>46</v>
@@ -1832,9 +1832,9 @@
       <c r="I30" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>9385</v>
+        <v>8469</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>12006</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-2621</v>
+        <v>-3537</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>46</v>
@@ -1877,9 +1877,9 @@
       <c r="I31" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>8469</v>
+        <v>9061</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>15205</v>
+        <v>12006</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-6736</v>
+        <v>-2945</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>46</v>
@@ -1922,9 +1922,9 @@
       <c r="I32" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>9427</v>
+        <v>9385</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>15205</v>
+        <v>12006</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-5778</v>
+        <v>-2621</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>46</v>
@@ -1967,9 +1967,9 @@
       <c r="I33" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>10048</v>
+        <v>8469</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>15205</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-5157</v>
+        <v>-6736</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-778</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>12092</v>
+        <v>9427</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>15205</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-3113</v>
+        <v>-5778</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,30 +2081,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-778</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>15756</v>
+        <v>11006</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>17601</v>
+        <v>15205</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-1845</v>
+        <v>-4199</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>19-AUG-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2130,13 +2130,13 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>15756</v>
+        <v>12092</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>17601</v>
+        <v>15205</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-1845</v>
+        <v>-3113</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>20</v>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>30-SEP-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>8582</v>
+        <v>7666</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>15205</v>
+        <v>10005</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-6623</v>
+        <v>-2339</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>46</v>
@@ -2327,9 +2327,9 @@
       <c r="I41" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>30-SEP-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>9427</v>
+        <v>8582</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>15205</v>
+        <v>10005</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-5778</v>
+        <v>-1423</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>46</v>
@@ -2372,147 +2372,12 @@
       <c r="I42" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>16-SEP-26</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-651</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>9427</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>15205</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>-5778</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>30-SEP-26</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-651</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>7666</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>10005</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>-2339</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>30-SEP-26</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-647</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>8582</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>10005</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>-1423</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,12 +58,6 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,12 +456,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -541,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-151</t>
+          <t>flynas XY-264</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3621</v>
+        <v>9340</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7934</v>
+        <v>15204</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4313</v>
+        <v>-5864</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -586,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-253</t>
+          <t>Nesma Airlines NE-160</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3621</v>
+        <v>11350</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7934</v>
+        <v>15204</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4313</v>
+        <v>-3854</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,26 +632,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-251</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3621</v>
+        <v>12872</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7934</v>
+        <v>15204</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4313</v>
+        <v>-2332</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -686,26 +677,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>Nesma Airlines NE-164</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>11823</v>
+        <v>9647</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13599</v>
+        <v>15204</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1776</v>
+        <v>-5557</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -731,26 +722,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>Nesma Airlines NE-160</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>12359</v>
+        <v>10345</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13599</v>
+        <v>15204</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1240</v>
+        <v>-4859</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -776,17 +767,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12359</v>
+        <v>12872</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13599</v>
+        <v>15204</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1240</v>
+        <v>-2332</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -825,13 +816,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9540</v>
+        <v>9074</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13599</v>
+        <v>13598</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-4059</v>
+        <v>-4524</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -870,13 +861,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10358</v>
+        <v>9884</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13599</v>
+        <v>13598</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-3241</v>
+        <v>-3714</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -915,13 +906,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10414</v>
+        <v>9926</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13599</v>
+        <v>13598</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-3185</v>
+        <v>-3672</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -932,9 +923,9 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +947,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9540</v>
+        <v>8739</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>12006</v>
+        <v>13598</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-2466</v>
+        <v>-4859</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -977,9 +968,9 @@
       <c r="I11" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +992,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10358</v>
+        <v>8963</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12006</v>
+        <v>13598</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-1648</v>
+        <v>-4635</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1022,9 +1013,9 @@
       <c r="I12" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1037,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10414</v>
+        <v>9074</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12006</v>
+        <v>13598</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-1592</v>
+        <v>-4524</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>46</v>
@@ -1067,9 +1058,9 @@
       <c r="I13" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1095,26 +1086,26 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9540</v>
+        <v>6115</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13599</v>
+        <v>10792</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4059</v>
+        <v>-4677</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1140,26 +1131,26 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10019</v>
+        <v>6589</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>13599</v>
+        <v>10792</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3580</v>
+        <v>-4203</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1172,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>10358</v>
+        <v>8153</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>13599</v>
+        <v>10792</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-3241</v>
+        <v>-2639</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1202,9 +1193,9 @@
       <c r="I16" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1230,22 +1221,22 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>9427</v>
+        <v>6003</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>10809</v>
+        <v>10792</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-1382</v>
+        <v>-4789</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1261,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,22 +1266,22 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>9540</v>
+        <v>6003</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>10809</v>
+        <v>10792</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-1269</v>
+        <v>-4789</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1320,22 +1311,22 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>10019</v>
+        <v>6589</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>10809</v>
+        <v>10792</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-790</v>
+        <v>-4203</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1351,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1365,13 +1356,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9427</v>
+        <v>8153</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>10005</v>
+        <v>9996</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-578</v>
+        <v>-1843</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1396,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>9427</v>
+        <v>8153</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>10005</v>
+        <v>9996</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-578</v>
+        <v>-1843</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1441,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1442,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>7666</v>
+        <v>9074</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>10809</v>
+        <v>9996</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-3143</v>
+        <v>-922</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1486,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1487,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8258</v>
+        <v>8153</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>10809</v>
+        <v>10792</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-2551</v>
+        <v>-2639</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1531,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1532,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>8469</v>
+        <v>8963</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10809</v>
+        <v>10792</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-2340</v>
+        <v>-1829</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1576,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,26 +1577,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>6863</v>
+        <v>9074</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>12006</v>
+        <v>10792</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-5143</v>
+        <v>-1718</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1621,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,26 +1622,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>6863</v>
+        <v>9549</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>12006</v>
+        <v>9996</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-5143</v>
+        <v>-447</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -1676,26 +1667,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-272</t>
+          <t>flyadeal F3-608</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>9202</v>
+        <v>5849</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>12006</v>
+        <v>11992</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-2804</v>
+        <v>-6143</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1725,22 +1716,22 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>6863</v>
+        <v>8153</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>13599</v>
+        <v>11992</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-6736</v>
+        <v>-3839</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -1756,7 +1747,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1757,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flynas XY-270</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>7666</v>
+        <v>9116</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>13599</v>
+        <v>11992</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-5933</v>
+        <v>-2876</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1811,30 +1802,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>flyadeal F3-606</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>8582</v>
+        <v>5849</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>13599</v>
+        <v>13598</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-5017</v>
+        <v>-7749</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1837,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1860,13 +1851,13 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8469</v>
+        <v>8153</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>12006</v>
+        <v>13598</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-3537</v>
+        <v>-5445</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>46</v>
@@ -1891,7 +1882,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,17 +1892,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>9061</v>
+        <v>9074</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>12006</v>
+        <v>13598</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-2945</v>
+        <v>-4524</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>46</v>
@@ -1922,9 +1913,9 @@
       <c r="I32" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1927,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,26 +1937,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>flyadeal F3-778</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>9385</v>
+        <v>11980</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>12006</v>
+        <v>13598</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-2621</v>
+        <v>-1618</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1981,7 +1972,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1995,13 +1986,13 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>8469</v>
+        <v>9926</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>15205</v>
+        <v>11992</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-6736</v>
+        <v>-2066</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>46</v>
@@ -2012,9 +2003,9 @@
       <c r="I34" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2017,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,17 +2027,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>9427</v>
+        <v>10848</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>15205</v>
+        <v>11992</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-5778</v>
+        <v>-1144</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>46</v>
@@ -2057,9 +2048,9 @@
       <c r="I35" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2062,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2072,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>11006</v>
+        <v>10917</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>15205</v>
+        <v>11992</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-4199</v>
+        <v>-1075</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>46</v>
@@ -2102,9 +2093,9 @@
       <c r="I36" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2126,17 +2117,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-778</t>
+          <t>Air Arabia Egypt E5-415</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>12092</v>
+        <v>7903</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>15205</v>
+        <v>15204</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-3113</v>
+        <v>-7301</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>20</v>
@@ -2147,9 +2138,9 @@
       <c r="I37" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2152,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,30 +2162,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-151</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>10076</v>
+        <v>9926</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>15205</v>
+        <v>15204</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-5129</v>
+        <v>-5278</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2197,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,30 +2207,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-251</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>10076</v>
+        <v>11504</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>15205</v>
+        <v>15204</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-5129</v>
+        <v>-3700</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2242,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,30 +2252,30 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-164</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>10358</v>
+        <v>9884</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>15205</v>
+        <v>15204</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-4847</v>
+        <v>-5320</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2296,7 +2287,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30-SEP-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,17 +2297,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>7666</v>
+        <v>9926</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>10005</v>
+        <v>15204</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-2339</v>
+        <v>-5278</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>46</v>
@@ -2327,9 +2318,9 @@
       <c r="I41" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,43 +2332,133 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>9926</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>15204</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-5278</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>30-SEP-26</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>SM-465</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>8153</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>9996</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-1843</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>30-SEP-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>EgyptAir MS-647</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
-        <v>8582</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>10005</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>-1423</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="D44" s="2" t="n">
+        <v>9074</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>9996</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-922</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_RUH_threats.xlsx
+++ b/excel_routes/route_ATZ_RUH_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -532,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-264</t>
+          <t>Nesma Airlines NE-164</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9340</v>
+        <v>8266</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>15204</v>
+        <v>13482</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-5864</v>
+        <v>-5216</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -577,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-160</t>
+          <t>Nile Air NP-251</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11350</v>
+        <v>9494</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>15204</v>
+        <v>13482</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3854</v>
+        <v>-3988</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -622,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>12872</v>
+        <v>9839</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15204</v>
+        <v>13482</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-2332</v>
+        <v>-3643</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -653,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9647</v>
+        <v>8266</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>15204</v>
+        <v>11895</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5557</v>
+        <v>-3629</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-160</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10345</v>
+        <v>9839</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15204</v>
+        <v>11895</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4859</v>
+        <v>-2056</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12872</v>
+        <v>9149</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>15204</v>
+        <v>15083</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-2332</v>
+        <v>-5934</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -788,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -816,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9074</v>
+        <v>9273</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13598</v>
+        <v>15083</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-4524</v>
+        <v>-5810</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>9884</v>
+        <v>9729</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13598</v>
+        <v>15083</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-3714</v>
+        <v>-5354</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -892,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>Nesma Airlines NE-160</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9926</v>
+        <v>6499</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13598</v>
+        <v>10695</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-3672</v>
+        <v>-4196</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8739</v>
+        <v>7976</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13598</v>
+        <v>10695</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-4859</v>
+        <v>-2719</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -968,9 +977,9 @@
       <c r="I11" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8963</v>
+        <v>7976</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13598</v>
+        <v>10695</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-4635</v>
+        <v>-2719</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1013,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1027,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9074</v>
+        <v>6927</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13598</v>
+        <v>9894</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4524</v>
+        <v>-2967</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>46</v>
@@ -1058,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1072,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,26 +1091,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6115</v>
+        <v>6927</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>10792</v>
+        <v>9894</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4677</v>
+        <v>-2967</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1117,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,26 +1136,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>6589</v>
+        <v>7507</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>10792</v>
+        <v>9894</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-4203</v>
+        <v>-2387</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1162,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1176,13 +1185,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8153</v>
+        <v>7396</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>10792</v>
+        <v>9080</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-2639</v>
+        <v>-1684</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1207,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6003</v>
+        <v>7396</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>10792</v>
+        <v>9080</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-4789</v>
+        <v>-1684</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1252,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6003</v>
+        <v>7824</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>10792</v>
+        <v>9080</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-4789</v>
+        <v>-1256</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>Nile Air NP-151</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6589</v>
+        <v>7093</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>10792</v>
+        <v>10695</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-4203</v>
+        <v>-3602</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1342,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1352,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>Nesma Airlines NE-160</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8153</v>
+        <v>7176</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>9996</v>
+        <v>10695</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-1843</v>
+        <v>-3519</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1387,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1397,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8153</v>
+        <v>9163</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>9996</v>
+        <v>10695</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-1843</v>
+        <v>-1532</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1432,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1442,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>9074</v>
+        <v>7396</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>9996</v>
+        <v>7824</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-922</v>
+        <v>-428</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1477,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1491,13 +1500,13 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8153</v>
+        <v>6927</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>10792</v>
+        <v>7327</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-2639</v>
+        <v>-400</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1522,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1536,13 +1545,13 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>8963</v>
+        <v>6927</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10792</v>
+        <v>7327</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-1829</v>
+        <v>-400</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1567,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1577,17 +1586,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>9074</v>
+        <v>6927</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>10792</v>
+        <v>8432</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-1718</v>
+        <v>-1505</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46</v>
@@ -1612,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1622,17 +1631,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>9549</v>
+        <v>6927</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>9996</v>
+        <v>8432</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-447</v>
+        <v>-1505</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46</v>
@@ -1657,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1667,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-608</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>5849</v>
+        <v>7396</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>11992</v>
+        <v>8432</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-6143</v>
+        <v>-1036</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1702,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1712,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>8153</v>
+        <v>7507</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>11992</v>
+        <v>8432</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-3839</v>
+        <v>-925</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>46</v>
@@ -1733,9 +1742,9 @@
       <c r="I28" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1747,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1757,26 +1766,26 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-270</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>9116</v>
+        <v>7824</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11992</v>
+        <v>8432</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-2876</v>
+        <v>-608</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1792,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1802,26 +1811,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-606</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>5849</v>
+        <v>7976</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>13598</v>
+        <v>9894</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-7749</v>
+        <v>-1918</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -1837,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1847,17 +1856,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>8153</v>
+        <v>7976</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>13598</v>
+        <v>9894</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-5445</v>
+        <v>-1918</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>46</v>
@@ -1868,9 +1877,9 @@
       <c r="I31" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1882,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1892,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>9074</v>
+        <v>7976</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>13598</v>
+        <v>9894</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-4524</v>
+        <v>-1918</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>46</v>
@@ -1913,9 +1922,9 @@
       <c r="I32" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1927,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1937,26 +1946,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-778</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>11980</v>
+        <v>6444</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>13598</v>
+        <v>11895</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-1618</v>
+        <v>-5451</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1972,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1982,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>9926</v>
+        <v>7396</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11992</v>
+        <v>11895</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-2066</v>
+        <v>-4499</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>46</v>
@@ -2003,9 +2012,9 @@
       <c r="I34" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2017,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2031,13 +2040,13 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>10848</v>
+        <v>7824</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>11992</v>
+        <v>11895</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-1144</v>
+        <v>-4071</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>46</v>
@@ -2048,9 +2057,9 @@
       <c r="I35" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2062,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2076,13 +2085,13 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>10917</v>
+        <v>7396</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>11992</v>
+        <v>13482</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-1075</v>
+        <v>-6086</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>46</v>
@@ -2093,9 +2102,9 @@
       <c r="I36" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2107,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2117,26 +2126,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-415</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>7903</v>
+        <v>7976</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>15204</v>
+        <v>13482</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-7301</v>
+        <v>-5506</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
@@ -2152,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2162,17 +2171,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>EgyptAir MS-647</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>9926</v>
+        <v>8307</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>15204</v>
+        <v>13482</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-5278</v>
+        <v>-5175</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>46</v>
@@ -2197,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2207,17 +2216,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-649</t>
+          <t>EgyptAir MS-689</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>11504</v>
+        <v>7976</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>15204</v>
+        <v>13482</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-3700</v>
+        <v>-5506</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>46</v>
@@ -2242,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2252,17 +2261,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-647</t>
+          <t>EgyptAir MS-649</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>9884</v>
+        <v>7976</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>15204</v>
+        <v>13482</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-5320</v>
+        <v>-5506</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>46</v>
@@ -2287,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2297,17 +2306,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-689</t>
+          <t>EgyptAir MS-651</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>9926</v>
+        <v>7976</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>15204</v>
+        <v>13482</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-5278</v>
+        <v>-5506</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>46</v>
@@ -2332,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2342,30 +2351,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flyadeal F3-778</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>9926</v>
+        <v>15430</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>15204</v>
+        <v>17471</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-5278</v>
+        <v>-2041</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2377,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>30-SEP-26</t>
+          <t>19-AUG-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2387,26 +2396,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-651</t>
+          <t>flyadeal F3-778</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>8153</v>
+        <v>15430</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>9996</v>
+        <v>17471</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-1843</v>
+        <v>-2041</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -2422,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2432,33 +2441,258 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>Saudia SV-312</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>8294</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>15083</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-6789</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-151</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>9963</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>15083</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-5120</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-251</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>9963</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>15083</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-5120</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
           <t>EgyptAir MS-647</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n">
-        <v>9074</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>9996</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>-922</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="D47" s="2" t="n">
+        <v>9260</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>15083</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-5823</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-689</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>9315</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>15083</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-5768</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-465</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-651</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>9315</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>15083</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-5768</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
